--- a/data/BallparkPal_Games.xlsx
+++ b/data/BallparkPal_Games.xlsx
@@ -140,12 +140,48 @@
     <t>2026-04-28</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
     <t xml:space="preserve">SF </t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>ARI</t>
   </si>
   <si>
@@ -170,64 +206,28 @@
     <t>CIN</t>
   </si>
   <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
     <t>HOU</t>
   </si>
   <si>
     <t>BAL</t>
   </si>
   <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
     <t xml:space="preserve">KC </t>
   </si>
   <si>
     <t>ATH</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>NYY</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>CHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD </t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>NYM</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>LAA</t>
-  </si>
-  <si>
-    <t>CHW</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>ATL</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
     </row>
     <row r="2" spans="1:40">
       <c r="A2">
-        <v>823473</v>
+        <v>822823</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -706,117 +706,117 @@
         <v>42</v>
       </c>
       <c r="E2">
-        <v>4.116</v>
+        <v>3.685</v>
       </c>
       <c r="F2">
-        <v>5.189</v>
+        <v>4.246</v>
       </c>
       <c r="G2">
-        <v>0.362</v>
+        <v>0.424</v>
       </c>
       <c r="H2">
-        <v>0.638</v>
+        <v>0.576</v>
       </c>
       <c r="I2">
-        <v>0.175</v>
+        <v>0.199</v>
       </c>
       <c r="J2">
-        <v>0.082</v>
+        <v>0.097</v>
       </c>
       <c r="K2">
-        <v>0.106</v>
+        <v>0.127</v>
       </c>
       <c r="L2">
-        <v>0.343</v>
+        <v>0.276</v>
       </c>
       <c r="M2">
-        <v>0.115</v>
+        <v>0.119</v>
       </c>
       <c r="N2">
-        <v>0.179</v>
+        <v>0.181</v>
       </c>
       <c r="O2">
-        <v>0.509</v>
+        <v>0.456</v>
       </c>
       <c r="P2">
-        <v>2.147</v>
+        <v>1.865</v>
       </c>
       <c r="Q2">
-        <v>3.086</v>
+        <v>2.548</v>
       </c>
       <c r="R2">
-        <v>0.311</v>
+        <v>0.327</v>
       </c>
       <c r="S2">
-        <v>0.551</v>
+        <v>0.5</v>
       </c>
       <c r="T2">
         <v>0.0</v>
       </c>
       <c r="U2">
-        <v>0.016</v>
+        <v>0.031</v>
       </c>
       <c r="V2">
+        <v>0.029</v>
+      </c>
+      <c r="W2">
+        <v>0.069</v>
+      </c>
+      <c r="X2">
+        <v>0.068</v>
+      </c>
+      <c r="Y2">
+        <v>0.121</v>
+      </c>
+      <c r="Z2">
+        <v>0.082</v>
+      </c>
+      <c r="AA2">
+        <v>0.112</v>
+      </c>
+      <c r="AB2">
+        <v>0.079</v>
+      </c>
+      <c r="AC2">
+        <v>0.097</v>
+      </c>
+      <c r="AD2">
+        <v>0.063</v>
+      </c>
+      <c r="AE2">
+        <v>0.068</v>
+      </c>
+      <c r="AF2">
+        <v>0.042</v>
+      </c>
+      <c r="AG2">
+        <v>0.042</v>
+      </c>
+      <c r="AH2">
+        <v>0.029</v>
+      </c>
+      <c r="AI2">
+        <v>0.025</v>
+      </c>
+      <c r="AJ2">
+        <v>0.012</v>
+      </c>
+      <c r="AK2">
         <v>0.014</v>
       </c>
-      <c r="W2">
-        <v>0.046</v>
-      </c>
-      <c r="X2">
-        <v>0.046</v>
-      </c>
-      <c r="Y2">
-        <v>0.087</v>
-      </c>
-      <c r="Z2">
-        <v>0.069</v>
-      </c>
-      <c r="AA2">
-        <v>0.103</v>
-      </c>
-      <c r="AB2">
-        <v>0.085</v>
-      </c>
-      <c r="AC2">
-        <v>0.107</v>
-      </c>
-      <c r="AD2">
-        <v>0.072</v>
-      </c>
-      <c r="AE2">
-        <v>0.08</v>
-      </c>
-      <c r="AF2">
-        <v>0.064</v>
-      </c>
-      <c r="AG2">
-        <v>0.051</v>
-      </c>
-      <c r="AH2">
-        <v>0.035</v>
-      </c>
-      <c r="AI2">
-        <v>0.031</v>
-      </c>
-      <c r="AJ2">
-        <v>0.023</v>
-      </c>
-      <c r="AK2">
-        <v>0.024</v>
-      </c>
       <c r="AL2">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AM2">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="AN2">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="3" spans="1:40">
       <c r="A3">
-        <v>823798</v>
+        <v>822908</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -828,117 +828,117 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>4.519</v>
+        <v>4.174</v>
       </c>
       <c r="F3">
-        <v>5.115</v>
+        <v>3.6</v>
       </c>
       <c r="G3">
-        <v>0.403</v>
+        <v>0.541</v>
       </c>
       <c r="H3">
-        <v>0.597</v>
+        <v>0.459</v>
       </c>
       <c r="I3">
-        <v>0.223</v>
+        <v>0.294</v>
       </c>
       <c r="J3">
-        <v>0.076</v>
+        <v>0.114</v>
       </c>
       <c r="K3">
-        <v>0.104</v>
+        <v>0.133</v>
       </c>
       <c r="L3">
-        <v>0.306</v>
+        <v>0.188</v>
       </c>
       <c r="M3">
-        <v>0.107</v>
+        <v>0.09</v>
       </c>
       <c r="N3">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="O3">
-        <v>0.564</v>
+        <v>0.418</v>
       </c>
       <c r="P3">
-        <v>2.448</v>
+        <v>1.944</v>
       </c>
       <c r="Q3">
-        <v>3.077</v>
+        <v>1.681</v>
       </c>
       <c r="R3">
-        <v>0.352</v>
+        <v>0.44</v>
       </c>
       <c r="S3">
-        <v>0.51</v>
+        <v>0.356</v>
       </c>
       <c r="T3">
         <v>0.0</v>
       </c>
       <c r="U3">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="V3">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="W3">
-        <v>0.044</v>
+        <v>0.086</v>
       </c>
       <c r="X3">
+        <v>0.073</v>
+      </c>
+      <c r="Y3">
+        <v>0.119</v>
+      </c>
+      <c r="Z3">
+        <v>0.082</v>
+      </c>
+      <c r="AA3">
+        <v>0.11</v>
+      </c>
+      <c r="AB3">
+        <v>0.071</v>
+      </c>
+      <c r="AC3">
+        <v>0.105</v>
+      </c>
+      <c r="AD3">
+        <v>0.057</v>
+      </c>
+      <c r="AE3">
+        <v>0.07</v>
+      </c>
+      <c r="AF3">
         <v>0.04</v>
       </c>
-      <c r="Y3">
-        <v>0.083</v>
-      </c>
-      <c r="Z3">
-        <v>0.065</v>
-      </c>
-      <c r="AA3">
-        <v>0.106</v>
-      </c>
-      <c r="AB3">
-        <v>0.084</v>
-      </c>
-      <c r="AC3">
-        <v>0.107</v>
-      </c>
-      <c r="AD3">
-        <v>0.071</v>
-      </c>
-      <c r="AE3">
-        <v>0.085</v>
-      </c>
-      <c r="AF3">
-        <v>0.055</v>
-      </c>
       <c r="AG3">
-        <v>0.056</v>
+        <v>0.04</v>
       </c>
       <c r="AH3">
-        <v>0.041</v>
+        <v>0.026</v>
       </c>
       <c r="AI3">
-        <v>0.046</v>
+        <v>0.018</v>
       </c>
       <c r="AJ3">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="AK3">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AN3">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="4" spans="1:40">
       <c r="A4">
-        <v>823956</v>
+        <v>823310</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
@@ -950,117 +950,117 @@
         <v>46</v>
       </c>
       <c r="E4">
-        <v>3.106</v>
+        <v>4.525</v>
       </c>
       <c r="F4">
-        <v>4.846</v>
+        <v>4.463</v>
       </c>
       <c r="G4">
-        <v>0.283</v>
+        <v>0.489</v>
       </c>
       <c r="H4">
-        <v>0.717</v>
+        <v>0.511</v>
       </c>
       <c r="I4">
-        <v>0.115</v>
+        <v>0.27</v>
       </c>
       <c r="J4">
-        <v>0.07</v>
+        <v>0.099</v>
       </c>
       <c r="K4">
+        <v>0.12</v>
+      </c>
+      <c r="L4">
+        <v>0.248</v>
+      </c>
+      <c r="M4">
         <v>0.098</v>
       </c>
-      <c r="L4">
-        <v>0.389</v>
-      </c>
-      <c r="M4">
-        <v>0.139</v>
-      </c>
       <c r="N4">
-        <v>0.189</v>
+        <v>0.165</v>
       </c>
       <c r="O4">
-        <v>0.491</v>
+        <v>0.475</v>
       </c>
       <c r="P4">
-        <v>1.523</v>
+        <v>2.53</v>
       </c>
       <c r="Q4">
-        <v>2.923</v>
+        <v>2.429</v>
       </c>
       <c r="R4">
-        <v>0.234</v>
+        <v>0.441</v>
       </c>
       <c r="S4">
-        <v>0.613</v>
+        <v>0.402</v>
       </c>
       <c r="T4">
         <v>0.0</v>
       </c>
       <c r="U4">
-        <v>0.025</v>
+        <v>0.013</v>
       </c>
       <c r="V4">
+        <v>0.015</v>
+      </c>
+      <c r="W4">
+        <v>0.055</v>
+      </c>
+      <c r="X4">
+        <v>0.042</v>
+      </c>
+      <c r="Y4">
+        <v>0.103</v>
+      </c>
+      <c r="Z4">
+        <v>0.073</v>
+      </c>
+      <c r="AA4">
+        <v>0.114</v>
+      </c>
+      <c r="AB4">
+        <v>0.085</v>
+      </c>
+      <c r="AC4">
+        <v>0.11</v>
+      </c>
+      <c r="AD4">
+        <v>0.075</v>
+      </c>
+      <c r="AE4">
+        <v>0.072</v>
+      </c>
+      <c r="AF4">
+        <v>0.043</v>
+      </c>
+      <c r="AG4">
+        <v>0.056</v>
+      </c>
+      <c r="AH4">
+        <v>0.037</v>
+      </c>
+      <c r="AI4">
         <v>0.028</v>
       </c>
-      <c r="W4">
-        <v>0.073</v>
-      </c>
-      <c r="X4">
-        <v>0.058</v>
-      </c>
-      <c r="Y4">
-        <v>0.115</v>
-      </c>
-      <c r="Z4">
-        <v>0.087</v>
-      </c>
-      <c r="AA4">
-        <v>0.126</v>
-      </c>
-      <c r="AB4">
-        <v>0.093</v>
-      </c>
-      <c r="AC4">
-        <v>0.095</v>
-      </c>
-      <c r="AD4">
-        <v>0.063</v>
-      </c>
-      <c r="AE4">
-        <v>0.068</v>
-      </c>
-      <c r="AF4">
-        <v>0.037</v>
-      </c>
-      <c r="AG4">
-        <v>0.046</v>
-      </c>
-      <c r="AH4">
-        <v>0.021</v>
-      </c>
-      <c r="AI4">
-        <v>0.023</v>
-      </c>
       <c r="AJ4">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="AK4">
+        <v>0.016</v>
+      </c>
+      <c r="AL4">
+        <v>0.013</v>
+      </c>
+      <c r="AM4">
         <v>0.012</v>
       </c>
-      <c r="AL4">
-        <v>0.005</v>
-      </c>
-      <c r="AM4">
-        <v>0.005</v>
-      </c>
       <c r="AN4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:40">
       <c r="A5">
-        <v>824447</v>
+        <v>823390</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
@@ -1072,117 +1072,117 @@
         <v>48</v>
       </c>
       <c r="E5">
-        <v>4.477</v>
+        <v>4.027</v>
       </c>
       <c r="F5">
-        <v>4.264</v>
+        <v>5.165</v>
       </c>
       <c r="G5">
-        <v>0.49</v>
+        <v>0.358</v>
       </c>
       <c r="H5">
-        <v>0.51</v>
+        <v>0.642</v>
       </c>
       <c r="I5">
-        <v>0.268</v>
+        <v>0.188</v>
       </c>
       <c r="J5">
-        <v>0.099</v>
+        <v>0.079</v>
       </c>
       <c r="K5">
-        <v>0.124</v>
+        <v>0.09</v>
       </c>
       <c r="L5">
-        <v>0.226</v>
+        <v>0.352</v>
       </c>
       <c r="M5">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="N5">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="O5">
-        <v>0.498</v>
+        <v>0.507</v>
       </c>
       <c r="P5">
-        <v>2.469</v>
+        <v>1.923</v>
       </c>
       <c r="Q5">
-        <v>2.356</v>
+        <v>3.061</v>
       </c>
       <c r="R5">
-        <v>0.431</v>
+        <v>0.283</v>
       </c>
       <c r="S5">
-        <v>0.417</v>
+        <v>0.565</v>
       </c>
       <c r="T5">
         <v>0.0</v>
       </c>
       <c r="U5">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="V5">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="W5">
-        <v>0.066</v>
+        <v>0.051</v>
       </c>
       <c r="X5">
-        <v>0.052</v>
+        <v>0.045</v>
       </c>
       <c r="Y5">
         <v>0.088</v>
       </c>
       <c r="Z5">
+        <v>0.078</v>
+      </c>
+      <c r="AA5">
+        <v>0.101</v>
+      </c>
+      <c r="AB5">
         <v>0.077</v>
       </c>
-      <c r="AA5">
-        <v>0.118</v>
-      </c>
-      <c r="AB5">
-        <v>0.076</v>
-      </c>
       <c r="AC5">
-        <v>0.102</v>
+        <v>0.093</v>
       </c>
       <c r="AD5">
-        <v>0.059</v>
+        <v>0.072</v>
       </c>
       <c r="AE5">
-        <v>0.093</v>
+        <v>0.085</v>
       </c>
       <c r="AF5">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="AG5">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="AH5">
         <v>0.033</v>
       </c>
       <c r="AI5">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AJ5">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="AK5">
+        <v>0.024</v>
+      </c>
+      <c r="AL5">
+        <v>0.012</v>
+      </c>
+      <c r="AM5">
+        <v>0.011</v>
+      </c>
+      <c r="AN5">
         <v>0.022</v>
-      </c>
-      <c r="AL5">
-        <v>0.007</v>
-      </c>
-      <c r="AM5">
-        <v>0.007</v>
-      </c>
-      <c r="AN5">
-        <v>0.012</v>
       </c>
     </row>
     <row r="6" spans="1:40">
       <c r="A6">
-        <v>824526</v>
+        <v>823473</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -1194,117 +1194,117 @@
         <v>50</v>
       </c>
       <c r="E6">
-        <v>4.134</v>
+        <v>4.254</v>
       </c>
       <c r="F6">
-        <v>4.854</v>
+        <v>5.151</v>
       </c>
       <c r="G6">
-        <v>0.401</v>
+        <v>0.384</v>
       </c>
       <c r="H6">
-        <v>0.599</v>
+        <v>0.616</v>
       </c>
       <c r="I6">
-        <v>0.201</v>
+        <v>0.197</v>
       </c>
       <c r="J6">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K6">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="L6">
-        <v>0.299</v>
+        <v>0.334</v>
       </c>
       <c r="M6">
-        <v>0.125</v>
+        <v>0.102</v>
       </c>
       <c r="N6">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="O6">
-        <v>0.471</v>
+        <v>0.511</v>
       </c>
       <c r="P6">
-        <v>1.954</v>
+        <v>2.207</v>
       </c>
       <c r="Q6">
-        <v>2.71</v>
+        <v>3.087</v>
       </c>
       <c r="R6">
         <v>0.323</v>
       </c>
       <c r="S6">
-        <v>0.525</v>
+        <v>0.536</v>
       </c>
       <c r="T6">
         <v>0.0</v>
       </c>
       <c r="U6">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="V6">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="W6">
+        <v>0.045</v>
+      </c>
+      <c r="X6">
+        <v>0.037</v>
+      </c>
+      <c r="Y6">
+        <v>0.091</v>
+      </c>
+      <c r="Z6">
+        <v>0.074</v>
+      </c>
+      <c r="AA6">
+        <v>0.109</v>
+      </c>
+      <c r="AB6">
+        <v>0.067</v>
+      </c>
+      <c r="AC6">
+        <v>0.101</v>
+      </c>
+      <c r="AD6">
+        <v>0.076</v>
+      </c>
+      <c r="AE6">
+        <v>0.082</v>
+      </c>
+      <c r="AF6">
+        <v>0.062</v>
+      </c>
+      <c r="AG6">
         <v>0.056</v>
       </c>
-      <c r="X6">
-        <v>0.054</v>
-      </c>
-      <c r="Y6">
-        <v>0.09</v>
-      </c>
-      <c r="Z6">
-        <v>0.071</v>
-      </c>
-      <c r="AA6">
-        <v>0.113</v>
-      </c>
-      <c r="AB6">
-        <v>0.079</v>
-      </c>
-      <c r="AC6">
-        <v>0.102</v>
-      </c>
-      <c r="AD6">
-        <v>0.08</v>
-      </c>
-      <c r="AE6">
-        <v>0.08</v>
-      </c>
-      <c r="AF6">
-        <v>0.052</v>
-      </c>
-      <c r="AG6">
-        <v>0.049</v>
-      </c>
       <c r="AH6">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="AI6">
-        <v>0.029</v>
+        <v>0.041</v>
       </c>
       <c r="AJ6">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AK6">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="AL6">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AM6">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="AN6">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="7" spans="1:40">
       <c r="A7">
-        <v>824849</v>
+        <v>823636</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
@@ -1316,117 +1316,117 @@
         <v>52</v>
       </c>
       <c r="E7">
-        <v>4.816</v>
+        <v>3.879</v>
       </c>
       <c r="F7">
-        <v>4.966</v>
+        <v>4.586</v>
       </c>
       <c r="G7">
-        <v>0.476</v>
+        <v>0.397</v>
       </c>
       <c r="H7">
-        <v>0.524</v>
+        <v>0.603</v>
       </c>
       <c r="I7">
-        <v>0.266</v>
+        <v>0.192</v>
       </c>
       <c r="J7">
-        <v>0.094</v>
+        <v>0.095</v>
       </c>
       <c r="K7">
-        <v>0.116</v>
+        <v>0.11</v>
       </c>
       <c r="L7">
-        <v>0.258</v>
+        <v>0.301</v>
       </c>
       <c r="M7">
-        <v>0.104</v>
+        <v>0.114</v>
       </c>
       <c r="N7">
-        <v>0.162</v>
+        <v>0.187</v>
       </c>
       <c r="O7">
-        <v>0.541</v>
+        <v>0.475</v>
       </c>
       <c r="P7">
-        <v>2.757</v>
+        <v>2.078</v>
       </c>
       <c r="Q7">
-        <v>2.856</v>
+        <v>2.679</v>
       </c>
       <c r="R7">
-        <v>0.437</v>
+        <v>0.357</v>
       </c>
       <c r="S7">
-        <v>0.432</v>
+        <v>0.491</v>
       </c>
       <c r="T7">
-        <v>0.001</v>
+        <v>0.0</v>
       </c>
       <c r="U7">
+        <v>0.016</v>
+      </c>
+      <c r="V7">
+        <v>0.018</v>
+      </c>
+      <c r="W7">
+        <v>0.061</v>
+      </c>
+      <c r="X7">
+        <v>0.057</v>
+      </c>
+      <c r="Y7">
+        <v>0.115</v>
+      </c>
+      <c r="Z7">
+        <v>0.089</v>
+      </c>
+      <c r="AA7">
+        <v>0.108</v>
+      </c>
+      <c r="AB7">
+        <v>0.086</v>
+      </c>
+      <c r="AC7">
+        <v>0.102</v>
+      </c>
+      <c r="AD7">
+        <v>0.065</v>
+      </c>
+      <c r="AE7">
+        <v>0.07</v>
+      </c>
+      <c r="AF7">
+        <v>0.049</v>
+      </c>
+      <c r="AG7">
+        <v>0.048</v>
+      </c>
+      <c r="AH7">
+        <v>0.026</v>
+      </c>
+      <c r="AI7">
+        <v>0.024</v>
+      </c>
+      <c r="AJ7">
+        <v>0.016</v>
+      </c>
+      <c r="AK7">
+        <v>0.02</v>
+      </c>
+      <c r="AL7">
+        <v>0.014</v>
+      </c>
+      <c r="AM7">
+        <v>0.006</v>
+      </c>
+      <c r="AN7">
         <v>0.01</v>
-      </c>
-      <c r="V7">
-        <v>0.014</v>
-      </c>
-      <c r="W7">
-        <v>0.036</v>
-      </c>
-      <c r="X7">
-        <v>0.04</v>
-      </c>
-      <c r="Y7">
-        <v>0.08</v>
-      </c>
-      <c r="Z7">
-        <v>0.06</v>
-      </c>
-      <c r="AA7">
-        <v>0.104</v>
-      </c>
-      <c r="AB7">
-        <v>0.079</v>
-      </c>
-      <c r="AC7">
-        <v>0.093</v>
-      </c>
-      <c r="AD7">
-        <v>0.082</v>
-      </c>
-      <c r="AE7">
-        <v>0.091</v>
-      </c>
-      <c r="AF7">
-        <v>0.051</v>
-      </c>
-      <c r="AG7">
-        <v>0.068</v>
-      </c>
-      <c r="AH7">
-        <v>0.033</v>
-      </c>
-      <c r="AI7">
-        <v>0.041</v>
-      </c>
-      <c r="AJ7">
-        <v>0.029</v>
-      </c>
-      <c r="AK7">
-        <v>0.029</v>
-      </c>
-      <c r="AL7">
-        <v>0.013</v>
-      </c>
-      <c r="AM7">
-        <v>0.015</v>
-      </c>
-      <c r="AN7">
-        <v>0.029</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8">
-        <v>825017</v>
+        <v>823716</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
@@ -1438,117 +1438,117 @@
         <v>54</v>
       </c>
       <c r="E8">
-        <v>4.904</v>
+        <v>4.39</v>
       </c>
       <c r="F8">
-        <v>4.648</v>
+        <v>4.161</v>
       </c>
       <c r="G8">
-        <v>0.502</v>
+        <v>0.506</v>
       </c>
       <c r="H8">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="I8">
-        <v>0.282</v>
+        <v>0.274</v>
       </c>
       <c r="J8">
-        <v>0.097</v>
+        <v>0.104</v>
       </c>
       <c r="K8">
-        <v>0.123</v>
+        <v>0.129</v>
       </c>
       <c r="L8">
-        <v>0.227</v>
+        <v>0.223</v>
       </c>
       <c r="M8">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="N8">
-        <v>0.168</v>
+        <v>0.164</v>
       </c>
       <c r="O8">
-        <v>0.528</v>
+        <v>0.474</v>
       </c>
       <c r="P8">
-        <v>2.548</v>
+        <v>2.21</v>
       </c>
       <c r="Q8">
-        <v>2.547</v>
+        <v>2.378</v>
       </c>
       <c r="R8">
-        <v>0.435</v>
+        <v>0.397</v>
       </c>
       <c r="S8">
-        <v>0.423</v>
+        <v>0.448</v>
       </c>
       <c r="T8">
         <v>0.0</v>
       </c>
       <c r="U8">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="V8">
+        <v>0.018</v>
+      </c>
+      <c r="W8">
+        <v>0.061</v>
+      </c>
+      <c r="X8">
+        <v>0.058</v>
+      </c>
+      <c r="Y8">
+        <v>0.101</v>
+      </c>
+      <c r="Z8">
+        <v>0.079</v>
+      </c>
+      <c r="AA8">
+        <v>0.116</v>
+      </c>
+      <c r="AB8">
+        <v>0.082</v>
+      </c>
+      <c r="AC8">
+        <v>0.108</v>
+      </c>
+      <c r="AD8">
+        <v>0.071</v>
+      </c>
+      <c r="AE8">
+        <v>0.074</v>
+      </c>
+      <c r="AF8">
+        <v>0.049</v>
+      </c>
+      <c r="AG8">
+        <v>0.043</v>
+      </c>
+      <c r="AH8">
+        <v>0.037</v>
+      </c>
+      <c r="AI8">
+        <v>0.029</v>
+      </c>
+      <c r="AJ8">
+        <v>0.019</v>
+      </c>
+      <c r="AK8">
+        <v>0.016</v>
+      </c>
+      <c r="AL8">
+        <v>0.007</v>
+      </c>
+      <c r="AM8">
+        <v>0.006</v>
+      </c>
+      <c r="AN8">
         <v>0.011</v>
-      </c>
-      <c r="W8">
-        <v>0.045</v>
-      </c>
-      <c r="X8">
-        <v>0.043</v>
-      </c>
-      <c r="Y8">
-        <v>0.084</v>
-      </c>
-      <c r="Z8">
-        <v>0.068</v>
-      </c>
-      <c r="AA8">
-        <v>0.105</v>
-      </c>
-      <c r="AB8">
-        <v>0.075</v>
-      </c>
-      <c r="AC8">
-        <v>0.104</v>
-      </c>
-      <c r="AD8">
-        <v>0.072</v>
-      </c>
-      <c r="AE8">
-        <v>0.095</v>
-      </c>
-      <c r="AF8">
-        <v>0.057</v>
-      </c>
-      <c r="AG8">
-        <v>0.055</v>
-      </c>
-      <c r="AH8">
-        <v>0.042</v>
-      </c>
-      <c r="AI8">
-        <v>0.035</v>
-      </c>
-      <c r="AJ8">
-        <v>0.022</v>
-      </c>
-      <c r="AK8">
-        <v>0.025</v>
-      </c>
-      <c r="AL8">
-        <v>0.013</v>
-      </c>
-      <c r="AM8">
-        <v>0.01</v>
-      </c>
-      <c r="AN8">
-        <v>0.028</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9">
-        <v>822823</v>
+        <v>823798</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1560,117 +1560,117 @@
         <v>56</v>
       </c>
       <c r="E9">
-        <v>3.636</v>
+        <v>4.325</v>
       </c>
       <c r="F9">
-        <v>4.232</v>
+        <v>4.746</v>
       </c>
       <c r="G9">
-        <v>0.421</v>
+        <v>0.425</v>
       </c>
       <c r="H9">
-        <v>0.579</v>
+        <v>0.575</v>
       </c>
       <c r="I9">
-        <v>0.199</v>
+        <v>0.225</v>
       </c>
       <c r="J9">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="K9">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="L9">
-        <v>0.284</v>
+        <v>0.297</v>
       </c>
       <c r="M9">
-        <v>0.117</v>
+        <v>0.107</v>
       </c>
       <c r="N9">
-        <v>0.178</v>
+        <v>0.17</v>
       </c>
       <c r="O9">
-        <v>0.436</v>
+        <v>0.514</v>
       </c>
       <c r="P9">
-        <v>1.805</v>
+        <v>2.284</v>
       </c>
       <c r="Q9">
-        <v>2.448</v>
+        <v>2.89</v>
       </c>
       <c r="R9">
-        <v>0.34</v>
+        <v>0.347</v>
       </c>
       <c r="S9">
-        <v>0.485</v>
+        <v>0.506</v>
       </c>
       <c r="T9">
         <v>0.0</v>
       </c>
       <c r="U9">
-        <v>0.025</v>
+        <v>0.013</v>
       </c>
       <c r="V9">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="W9">
+        <v>0.059</v>
+      </c>
+      <c r="X9">
+        <v>0.046</v>
+      </c>
+      <c r="Y9">
+        <v>0.091</v>
+      </c>
+      <c r="Z9">
+        <v>0.074</v>
+      </c>
+      <c r="AA9">
+        <v>0.116</v>
+      </c>
+      <c r="AB9">
         <v>0.077</v>
       </c>
-      <c r="X9">
-        <v>0.07</v>
-      </c>
-      <c r="Y9">
-        <v>0.115</v>
-      </c>
-      <c r="Z9">
-        <v>0.078</v>
-      </c>
-      <c r="AA9">
-        <v>0.126</v>
-      </c>
-      <c r="AB9">
-        <v>0.089</v>
-      </c>
       <c r="AC9">
-        <v>0.088</v>
+        <v>0.106</v>
       </c>
       <c r="AD9">
-        <v>0.062</v>
+        <v>0.071</v>
       </c>
       <c r="AE9">
-        <v>0.069</v>
+        <v>0.072</v>
       </c>
       <c r="AF9">
+        <v>0.057</v>
+      </c>
+      <c r="AG9">
+        <v>0.056</v>
+      </c>
+      <c r="AH9">
+        <v>0.03</v>
+      </c>
+      <c r="AI9">
         <v>0.036</v>
       </c>
-      <c r="AG9">
-        <v>0.039</v>
-      </c>
-      <c r="AH9">
+      <c r="AJ9">
         <v>0.02</v>
       </c>
-      <c r="AI9">
-        <v>0.026</v>
-      </c>
-      <c r="AJ9">
-        <v>0.015</v>
-      </c>
       <c r="AK9">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AL9">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="AM9">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="AN9">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10" spans="1:40">
       <c r="A10">
-        <v>822908</v>
+        <v>823956</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1682,109 +1682,109 @@
         <v>58</v>
       </c>
       <c r="E10">
-        <v>4.186</v>
+        <v>3.285</v>
       </c>
       <c r="F10">
-        <v>3.599</v>
+        <v>4.603</v>
       </c>
       <c r="G10">
-        <v>0.534</v>
+        <v>0.335</v>
       </c>
       <c r="H10">
-        <v>0.466</v>
+        <v>0.665</v>
       </c>
       <c r="I10">
-        <v>0.295</v>
+        <v>0.147</v>
       </c>
       <c r="J10">
-        <v>0.108</v>
+        <v>0.077</v>
       </c>
       <c r="K10">
-        <v>0.131</v>
+        <v>0.111</v>
       </c>
       <c r="L10">
-        <v>0.185</v>
+        <v>0.344</v>
       </c>
       <c r="M10">
-        <v>0.098</v>
+        <v>0.124</v>
       </c>
       <c r="N10">
-        <v>0.182</v>
+        <v>0.196</v>
       </c>
       <c r="O10">
-        <v>0.42</v>
+        <v>0.453</v>
       </c>
       <c r="P10">
-        <v>1.982</v>
+        <v>1.602</v>
       </c>
       <c r="Q10">
-        <v>1.679</v>
+        <v>2.675</v>
       </c>
       <c r="R10">
-        <v>0.448</v>
+        <v>0.275</v>
       </c>
       <c r="S10">
-        <v>0.352</v>
+        <v>0.562</v>
       </c>
       <c r="T10">
-        <v>0.0</v>
+        <v>0.001</v>
       </c>
       <c r="U10">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="V10">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="W10">
-        <v>0.087</v>
+        <v>0.078</v>
       </c>
       <c r="X10">
-        <v>0.067</v>
+        <v>0.058</v>
       </c>
       <c r="Y10">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="Z10">
+        <v>0.086</v>
+      </c>
+      <c r="AA10">
+        <v>0.124</v>
+      </c>
+      <c r="AB10">
         <v>0.085</v>
       </c>
-      <c r="AA10">
-        <v>0.12</v>
-      </c>
-      <c r="AB10">
-        <v>0.082</v>
-      </c>
       <c r="AC10">
-        <v>0.094</v>
+        <v>0.097</v>
       </c>
       <c r="AD10">
-        <v>0.069</v>
+        <v>0.066</v>
       </c>
       <c r="AE10">
-        <v>0.062</v>
+        <v>0.054</v>
       </c>
       <c r="AF10">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="AG10">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AH10">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AI10">
         <v>0.023</v>
       </c>
       <c r="AJ10">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="AK10">
         <v>0.009</v>
       </c>
       <c r="AL10">
+        <v>0.004</v>
+      </c>
+      <c r="AM10">
         <v>0.005</v>
-      </c>
-      <c r="AM10">
-        <v>0.004</v>
       </c>
       <c r="AN10">
         <v>0.008</v>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="11" spans="1:40">
       <c r="A11">
-        <v>823310</v>
+        <v>824447</v>
       </c>
       <c r="B11" t="s">
         <v>40</v>
@@ -1804,117 +1804,117 @@
         <v>60</v>
       </c>
       <c r="E11">
-        <v>4.549</v>
+        <v>4.644</v>
       </c>
       <c r="F11">
-        <v>4.712</v>
+        <v>4.489</v>
       </c>
       <c r="G11">
-        <v>0.466</v>
+        <v>0.487</v>
       </c>
       <c r="H11">
-        <v>0.534</v>
+        <v>0.513</v>
       </c>
       <c r="I11">
-        <v>0.25</v>
+        <v>0.272</v>
       </c>
       <c r="J11">
-        <v>0.094</v>
+        <v>0.098</v>
       </c>
       <c r="K11">
-        <v>0.122</v>
+        <v>0.118</v>
       </c>
       <c r="L11">
-        <v>0.269</v>
+        <v>0.245</v>
       </c>
       <c r="M11">
-        <v>0.097</v>
+        <v>0.102</v>
       </c>
       <c r="N11">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="O11">
-        <v>0.516</v>
+        <v>0.514</v>
       </c>
       <c r="P11">
-        <v>2.597</v>
+        <v>2.565</v>
       </c>
       <c r="Q11">
-        <v>2.704</v>
+        <v>2.551</v>
       </c>
       <c r="R11">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="S11">
-        <v>0.44</v>
+        <v>0.424</v>
       </c>
       <c r="T11">
         <v>0.0</v>
       </c>
       <c r="U11">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="V11">
         <v>0.013</v>
       </c>
       <c r="W11">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="X11">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="Y11">
-        <v>0.085</v>
+        <v>0.09</v>
       </c>
       <c r="Z11">
-        <v>0.071</v>
+        <v>0.076</v>
       </c>
       <c r="AA11">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="AB11">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="AC11">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="AD11">
-        <v>0.068</v>
+        <v>0.064</v>
       </c>
       <c r="AE11">
-        <v>0.087</v>
+        <v>0.082</v>
       </c>
       <c r="AF11">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="AG11">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="AH11">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="AI11">
         <v>0.034</v>
       </c>
       <c r="AJ11">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AK11">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AL11">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AM11">
         <v>0.012</v>
       </c>
       <c r="AN11">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" spans="1:40">
       <c r="A12">
-        <v>823390</v>
+        <v>824526</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
@@ -1926,117 +1926,117 @@
         <v>62</v>
       </c>
       <c r="E12">
-        <v>3.735</v>
+        <v>4.134</v>
       </c>
       <c r="F12">
-        <v>4.987</v>
+        <v>4.854</v>
       </c>
       <c r="G12">
-        <v>0.344</v>
+        <v>0.401</v>
       </c>
       <c r="H12">
-        <v>0.656</v>
+        <v>0.599</v>
       </c>
       <c r="I12">
-        <v>0.168</v>
+        <v>0.201</v>
       </c>
       <c r="J12">
-        <v>0.075</v>
+        <v>0.09</v>
       </c>
       <c r="K12">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="L12">
-        <v>0.339</v>
+        <v>0.299</v>
       </c>
       <c r="M12">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="N12">
-        <v>0.202</v>
+        <v>0.175</v>
       </c>
       <c r="O12">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="P12">
-        <v>1.786</v>
+        <v>1.954</v>
       </c>
       <c r="Q12">
-        <v>2.861</v>
+        <v>2.71</v>
       </c>
       <c r="R12">
-        <v>0.283</v>
+        <v>0.323</v>
       </c>
       <c r="S12">
-        <v>0.556</v>
+        <v>0.525</v>
       </c>
       <c r="T12">
         <v>0.0</v>
       </c>
       <c r="U12">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="V12">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="W12">
-        <v>0.069</v>
+        <v>0.056</v>
       </c>
       <c r="X12">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="Y12">
         <v>0.09</v>
       </c>
       <c r="Z12">
-        <v>0.075</v>
+        <v>0.071</v>
       </c>
       <c r="AA12">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
       <c r="AB12">
-        <v>0.071</v>
+        <v>0.079</v>
       </c>
       <c r="AC12">
-        <v>0.1</v>
+        <v>0.102</v>
       </c>
       <c r="AD12">
-        <v>0.066</v>
+        <v>0.08</v>
       </c>
       <c r="AE12">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="AF12">
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="AG12">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AH12">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="AI12">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="AJ12">
+        <v>0.021</v>
+      </c>
+      <c r="AK12">
         <v>0.019</v>
-      </c>
-      <c r="AK12">
-        <v>0.023</v>
       </c>
       <c r="AL12">
         <v>0.009</v>
       </c>
       <c r="AM12">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="AN12">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="13" spans="1:40">
       <c r="A13">
-        <v>823636</v>
+        <v>824610</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
@@ -2048,117 +2048,117 @@
         <v>64</v>
       </c>
       <c r="E13">
-        <v>3.892</v>
+        <v>4.966</v>
       </c>
       <c r="F13">
-        <v>4.627</v>
+        <v>3.503</v>
       </c>
       <c r="G13">
-        <v>0.393</v>
+        <v>0.629</v>
       </c>
       <c r="H13">
-        <v>0.607</v>
+        <v>0.371</v>
       </c>
       <c r="I13">
-        <v>0.194</v>
+        <v>0.395</v>
       </c>
       <c r="J13">
-        <v>0.082</v>
+        <v>0.1</v>
       </c>
       <c r="K13">
-        <v>0.116</v>
+        <v>0.134</v>
       </c>
       <c r="L13">
-        <v>0.294</v>
+        <v>0.145</v>
       </c>
       <c r="M13">
-        <v>0.132</v>
+        <v>0.076</v>
       </c>
       <c r="N13">
-        <v>0.181</v>
+        <v>0.15</v>
       </c>
       <c r="O13">
-        <v>0.461</v>
+        <v>0.484</v>
       </c>
       <c r="P13">
-        <v>2.138</v>
+        <v>2.76</v>
       </c>
       <c r="Q13">
-        <v>2.681</v>
+        <v>1.722</v>
       </c>
       <c r="R13">
-        <v>0.347</v>
+        <v>0.563</v>
       </c>
       <c r="S13">
-        <v>0.492</v>
+        <v>0.289</v>
       </c>
       <c r="T13">
         <v>0.0</v>
       </c>
       <c r="U13">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="V13">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="W13">
+        <v>0.063</v>
+      </c>
+      <c r="X13">
         <v>0.06</v>
       </c>
-      <c r="X13">
-        <v>0.057</v>
-      </c>
       <c r="Y13">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="Z13">
-        <v>0.083</v>
+        <v>0.084</v>
       </c>
       <c r="AA13">
-        <v>0.107</v>
+        <v>0.115</v>
       </c>
       <c r="AB13">
-        <v>0.088</v>
+        <v>0.079</v>
       </c>
       <c r="AC13">
-        <v>0.1</v>
+        <v>0.106</v>
       </c>
       <c r="AD13">
-        <v>0.072</v>
+        <v>0.067</v>
       </c>
       <c r="AE13">
-        <v>0.073</v>
+        <v>0.067</v>
       </c>
       <c r="AF13">
         <v>0.046</v>
       </c>
       <c r="AG13">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
       <c r="AH13">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="AI13">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="AJ13">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AK13">
         <v>0.015</v>
       </c>
       <c r="AL13">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="AM13">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AN13">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14" spans="1:40">
       <c r="A14">
-        <v>823716</v>
+        <v>824849</v>
       </c>
       <c r="B14" t="s">
         <v>40</v>
@@ -2170,117 +2170,117 @@
         <v>66</v>
       </c>
       <c r="E14">
-        <v>4.416</v>
+        <v>4.584</v>
       </c>
       <c r="F14">
-        <v>4.306</v>
+        <v>4.721</v>
       </c>
       <c r="G14">
-        <v>0.484</v>
+        <v>0.471</v>
       </c>
       <c r="H14">
-        <v>0.516</v>
+        <v>0.529</v>
       </c>
       <c r="I14">
-        <v>0.262</v>
+        <v>0.25</v>
       </c>
       <c r="J14">
-        <v>0.107</v>
+        <v>0.099</v>
       </c>
       <c r="K14">
-        <v>0.116</v>
+        <v>0.121</v>
       </c>
       <c r="L14">
-        <v>0.237</v>
+        <v>0.252</v>
       </c>
       <c r="M14">
-        <v>0.098</v>
+        <v>0.106</v>
       </c>
       <c r="N14">
-        <v>0.181</v>
+        <v>0.171</v>
       </c>
       <c r="O14">
-        <v>0.471</v>
+        <v>0.524</v>
       </c>
       <c r="P14">
-        <v>2.26</v>
+        <v>2.666</v>
       </c>
       <c r="Q14">
-        <v>2.425</v>
+        <v>2.694</v>
       </c>
       <c r="R14">
-        <v>0.411</v>
+        <v>0.432</v>
       </c>
       <c r="S14">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="T14">
         <v>0.0</v>
       </c>
       <c r="U14">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="V14">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="W14">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="X14">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="Y14">
+        <v>0.076</v>
+      </c>
+      <c r="Z14">
+        <v>0.071</v>
+      </c>
+      <c r="AA14">
+        <v>0.11</v>
+      </c>
+      <c r="AB14">
+        <v>0.077</v>
+      </c>
+      <c r="AC14">
         <v>0.105</v>
       </c>
-      <c r="Z14">
-        <v>0.079</v>
-      </c>
-      <c r="AA14">
-        <v>0.114</v>
-      </c>
-      <c r="AB14">
-        <v>0.071</v>
-      </c>
-      <c r="AC14">
-        <v>0.115</v>
-      </c>
       <c r="AD14">
-        <v>0.071</v>
+        <v>0.07</v>
       </c>
       <c r="AE14">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="AF14">
-        <v>0.049</v>
+        <v>0.053</v>
       </c>
       <c r="AG14">
-        <v>0.053</v>
+        <v>0.065</v>
       </c>
       <c r="AH14">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AI14">
-        <v>0.028</v>
+        <v>0.035</v>
       </c>
       <c r="AJ14">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="AK14">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AL14">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AM14">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="AN14">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="15" spans="1:40">
       <c r="A15">
-        <v>824610</v>
+        <v>824931</v>
       </c>
       <c r="B15" t="s">
         <v>40</v>
@@ -2292,117 +2292,117 @@
         <v>68</v>
       </c>
       <c r="E15">
-        <v>5.236</v>
+        <v>5.112</v>
       </c>
       <c r="F15">
-        <v>3.845</v>
+        <v>4.7</v>
       </c>
       <c r="G15">
-        <v>0.616</v>
+        <v>0.522</v>
       </c>
       <c r="H15">
-        <v>0.384</v>
+        <v>0.478</v>
       </c>
       <c r="I15">
-        <v>0.383</v>
+        <v>0.298</v>
       </c>
       <c r="J15">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="K15">
-        <v>0.127</v>
+        <v>0.123</v>
       </c>
       <c r="L15">
-        <v>0.157</v>
+        <v>0.222</v>
       </c>
       <c r="M15">
-        <v>0.076</v>
+        <v>0.097</v>
       </c>
       <c r="N15">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
       <c r="O15">
-        <v>0.496</v>
+        <v>0.522</v>
       </c>
       <c r="P15">
-        <v>2.93</v>
+        <v>2.878</v>
       </c>
       <c r="Q15">
-        <v>1.897</v>
+        <v>2.587</v>
       </c>
       <c r="R15">
-        <v>0.565</v>
+        <v>0.466</v>
       </c>
       <c r="S15">
-        <v>0.291</v>
+        <v>0.395</v>
       </c>
       <c r="T15">
         <v>0.0</v>
       </c>
       <c r="U15">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="V15">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="W15">
-        <v>0.055</v>
+        <v>0.042</v>
       </c>
       <c r="X15">
-        <v>0.047</v>
+        <v>0.035</v>
       </c>
       <c r="Y15">
-        <v>0.09</v>
+        <v>0.075</v>
       </c>
       <c r="Z15">
-        <v>0.073</v>
+        <v>0.059</v>
       </c>
       <c r="AA15">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="AB15">
-        <v>0.084</v>
+        <v>0.077</v>
       </c>
       <c r="AC15">
-        <v>0.097</v>
+        <v>0.108</v>
       </c>
       <c r="AD15">
         <v>0.073</v>
       </c>
       <c r="AE15">
-        <v>0.081</v>
+        <v>0.086</v>
       </c>
       <c r="AF15">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="AG15">
-        <v>0.055</v>
+        <v>0.065</v>
       </c>
       <c r="AH15">
-        <v>0.039</v>
+        <v>0.042</v>
       </c>
       <c r="AI15">
-        <v>0.036</v>
+        <v>0.041</v>
       </c>
       <c r="AJ15">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="AK15">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="AL15">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AM15">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="AN15">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="16" spans="1:40">
       <c r="A16">
-        <v>824931</v>
+        <v>825017</v>
       </c>
       <c r="B16" t="s">
         <v>40</v>
@@ -2414,49 +2414,49 @@
         <v>70</v>
       </c>
       <c r="E16">
-        <v>5.05</v>
+        <v>4.899</v>
       </c>
       <c r="F16">
-        <v>4.773</v>
+        <v>4.705</v>
       </c>
       <c r="G16">
-        <v>0.509</v>
+        <v>0.494</v>
       </c>
       <c r="H16">
-        <v>0.491</v>
+        <v>0.506</v>
       </c>
       <c r="I16">
-        <v>0.287</v>
+        <v>0.285</v>
       </c>
       <c r="J16">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="K16">
-        <v>0.124</v>
+        <v>0.115</v>
       </c>
       <c r="L16">
-        <v>0.232</v>
+        <v>0.234</v>
       </c>
       <c r="M16">
-        <v>0.084</v>
+        <v>0.103</v>
       </c>
       <c r="N16">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="O16">
-        <v>0.528</v>
+        <v>0.522</v>
       </c>
       <c r="P16">
-        <v>2.881</v>
+        <v>2.549</v>
       </c>
       <c r="Q16">
-        <v>2.583</v>
+        <v>2.573</v>
       </c>
       <c r="R16">
-        <v>0.475</v>
+        <v>0.428</v>
       </c>
       <c r="S16">
-        <v>0.387</v>
+        <v>0.423</v>
       </c>
       <c r="T16">
         <v>0.0</v>
@@ -2465,37 +2465,37 @@
         <v>0.011</v>
       </c>
       <c r="V16">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="W16">
-        <v>0.041</v>
+        <v>0.046</v>
       </c>
       <c r="X16">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="Y16">
+        <v>0.081</v>
+      </c>
+      <c r="Z16">
+        <v>0.072</v>
+      </c>
+      <c r="AA16">
+        <v>0.108</v>
+      </c>
+      <c r="AB16">
+        <v>0.081</v>
+      </c>
+      <c r="AC16">
+        <v>0.099</v>
+      </c>
+      <c r="AD16">
+        <v>0.068</v>
+      </c>
+      <c r="AE16">
         <v>0.077</v>
       </c>
-      <c r="Z16">
-        <v>0.057</v>
-      </c>
-      <c r="AA16">
-        <v>0.106</v>
-      </c>
-      <c r="AB16">
-        <v>0.077</v>
-      </c>
-      <c r="AC16">
-        <v>0.118</v>
-      </c>
-      <c r="AD16">
-        <v>0.071</v>
-      </c>
-      <c r="AE16">
-        <v>0.089</v>
-      </c>
       <c r="AF16">
-        <v>0.062</v>
+        <v>0.055</v>
       </c>
       <c r="AG16">
         <v>0.066</v>
@@ -2504,22 +2504,22 @@
         <v>0.043</v>
       </c>
       <c r="AI16">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="AJ16">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="AK16">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="AL16">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AM16">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="AN16">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
     </row>
   </sheetData>

--- a/data/BallparkPal_Games.xlsx
+++ b/data/BallparkPal_Games.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>GamePk</t>
   </si>
@@ -137,48 +137,30 @@
     <t>Runs20</t>
   </si>
   <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>BOS</t>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>NYM</t>
   </si>
   <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>NYY</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>CHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD </t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF </t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>NYM</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
@@ -188,28 +170,10 @@
     <t>MIL</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB </t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
     <t>COL</t>
   </si>
   <si>
     <t>CIN</t>
-  </si>
-  <si>
-    <t>LAA</t>
-  </si>
-  <si>
-    <t>CHW</t>
   </si>
   <si>
     <t>HOU</t>
@@ -567,7 +531,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -694,7 +658,7 @@
     </row>
     <row r="2" spans="1:40">
       <c r="A2">
-        <v>822823</v>
+        <v>823391</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -706,109 +670,109 @@
         <v>42</v>
       </c>
       <c r="E2">
-        <v>3.685</v>
+        <v>3.155</v>
       </c>
       <c r="F2">
-        <v>4.246</v>
+        <v>4.49</v>
       </c>
       <c r="G2">
-        <v>0.424</v>
+        <v>0.341</v>
       </c>
       <c r="H2">
-        <v>0.576</v>
+        <v>0.659</v>
       </c>
       <c r="I2">
-        <v>0.199</v>
+        <v>0.144</v>
       </c>
       <c r="J2">
-        <v>0.097</v>
+        <v>0.083</v>
       </c>
       <c r="K2">
-        <v>0.127</v>
+        <v>0.113</v>
       </c>
       <c r="L2">
-        <v>0.276</v>
+        <v>0.346</v>
       </c>
       <c r="M2">
-        <v>0.119</v>
+        <v>0.126</v>
       </c>
       <c r="N2">
-        <v>0.181</v>
+        <v>0.188</v>
       </c>
       <c r="O2">
-        <v>0.456</v>
+        <v>0.43</v>
       </c>
       <c r="P2">
-        <v>1.865</v>
+        <v>1.35</v>
       </c>
       <c r="Q2">
-        <v>2.548</v>
+        <v>2.556</v>
       </c>
       <c r="R2">
-        <v>0.327</v>
+        <v>0.253</v>
       </c>
       <c r="S2">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T2">
         <v>0.0</v>
       </c>
       <c r="U2">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="V2">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="W2">
-        <v>0.069</v>
+        <v>0.087</v>
       </c>
       <c r="X2">
-        <v>0.068</v>
+        <v>0.061</v>
       </c>
       <c r="Y2">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="Z2">
+        <v>0.094</v>
+      </c>
+      <c r="AA2">
+        <v>0.116</v>
+      </c>
+      <c r="AB2">
         <v>0.082</v>
       </c>
-      <c r="AA2">
-        <v>0.112</v>
-      </c>
-      <c r="AB2">
-        <v>0.079</v>
-      </c>
       <c r="AC2">
-        <v>0.097</v>
+        <v>0.092</v>
       </c>
       <c r="AD2">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="AE2">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="AF2">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="AG2">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AH2">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
       <c r="AI2">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="AJ2">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AK2">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AL2">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AN2">
         <v>0.007</v>
@@ -816,7 +780,7 @@
     </row>
     <row r="3" spans="1:40">
       <c r="A3">
-        <v>822908</v>
+        <v>823471</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -828,1698 +792,1210 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>4.174</v>
+        <v>4.782</v>
       </c>
       <c r="F3">
-        <v>3.6</v>
+        <v>5.568</v>
       </c>
       <c r="G3">
-        <v>0.541</v>
+        <v>0.395</v>
       </c>
       <c r="H3">
-        <v>0.459</v>
+        <v>0.605</v>
       </c>
       <c r="I3">
-        <v>0.294</v>
+        <v>0.225</v>
       </c>
       <c r="J3">
-        <v>0.114</v>
+        <v>0.071</v>
       </c>
       <c r="K3">
-        <v>0.133</v>
+        <v>0.099</v>
       </c>
       <c r="L3">
-        <v>0.188</v>
+        <v>0.344</v>
       </c>
       <c r="M3">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="N3">
-        <v>0.18</v>
+        <v>0.168</v>
       </c>
       <c r="O3">
-        <v>0.418</v>
+        <v>0.557</v>
       </c>
       <c r="P3">
-        <v>1.944</v>
+        <v>2.722</v>
       </c>
       <c r="Q3">
-        <v>1.681</v>
+        <v>3.438</v>
       </c>
       <c r="R3">
-        <v>0.44</v>
+        <v>0.362</v>
       </c>
       <c r="S3">
-        <v>0.356</v>
+        <v>0.524</v>
       </c>
       <c r="T3">
         <v>0.0</v>
       </c>
       <c r="U3">
+        <v>0.01</v>
+      </c>
+      <c r="V3">
+        <v>0.008</v>
+      </c>
+      <c r="W3">
+        <v>0.029</v>
+      </c>
+      <c r="X3">
+        <v>0.033</v>
+      </c>
+      <c r="Y3">
+        <v>0.066</v>
+      </c>
+      <c r="Z3">
+        <v>0.054</v>
+      </c>
+      <c r="AA3">
+        <v>0.099</v>
+      </c>
+      <c r="AB3">
+        <v>0.065</v>
+      </c>
+      <c r="AC3">
+        <v>0.103</v>
+      </c>
+      <c r="AD3">
+        <v>0.08</v>
+      </c>
+      <c r="AE3">
+        <v>0.084</v>
+      </c>
+      <c r="AF3">
+        <v>0.063</v>
+      </c>
+      <c r="AG3">
+        <v>0.084</v>
+      </c>
+      <c r="AH3">
+        <v>0.044</v>
+      </c>
+      <c r="AI3">
+        <v>0.05</v>
+      </c>
+      <c r="AJ3">
         <v>0.03</v>
       </c>
-      <c r="V3">
-        <v>0.03</v>
-      </c>
-      <c r="W3">
-        <v>0.086</v>
-      </c>
-      <c r="X3">
-        <v>0.073</v>
-      </c>
-      <c r="Y3">
-        <v>0.119</v>
-      </c>
-      <c r="Z3">
-        <v>0.082</v>
-      </c>
-      <c r="AA3">
-        <v>0.11</v>
-      </c>
-      <c r="AB3">
-        <v>0.071</v>
-      </c>
-      <c r="AC3">
-        <v>0.105</v>
-      </c>
-      <c r="AD3">
-        <v>0.057</v>
-      </c>
-      <c r="AE3">
-        <v>0.07</v>
-      </c>
-      <c r="AF3">
-        <v>0.04</v>
-      </c>
-      <c r="AG3">
-        <v>0.04</v>
-      </c>
-      <c r="AH3">
+      <c r="AK3">
         <v>0.026</v>
       </c>
-      <c r="AI3">
-        <v>0.018</v>
-      </c>
-      <c r="AJ3">
-        <v>0.011</v>
-      </c>
-      <c r="AK3">
-        <v>0.011</v>
-      </c>
       <c r="AL3">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="AM3">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="AN3">
-        <v>0.008</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="4" spans="1:40">
       <c r="A4">
-        <v>823310</v>
+        <v>823472</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4">
-        <v>4.525</v>
+        <v>3.638</v>
       </c>
       <c r="F4">
-        <v>4.463</v>
+        <v>4.264</v>
       </c>
       <c r="G4">
-        <v>0.489</v>
+        <v>0.399</v>
       </c>
       <c r="H4">
-        <v>0.511</v>
+        <v>0.601</v>
       </c>
       <c r="I4">
-        <v>0.27</v>
+        <v>0.181</v>
       </c>
       <c r="J4">
-        <v>0.099</v>
+        <v>0.104</v>
       </c>
       <c r="K4">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="L4">
-        <v>0.248</v>
+        <v>0.279</v>
       </c>
       <c r="M4">
-        <v>0.098</v>
+        <v>0.124</v>
       </c>
       <c r="N4">
-        <v>0.165</v>
+        <v>0.198</v>
       </c>
       <c r="O4">
-        <v>0.475</v>
+        <v>0.418</v>
       </c>
       <c r="P4">
-        <v>2.53</v>
+        <v>1.839</v>
       </c>
       <c r="Q4">
-        <v>2.429</v>
+        <v>2.385</v>
       </c>
       <c r="R4">
-        <v>0.441</v>
+        <v>0.326</v>
       </c>
       <c r="S4">
-        <v>0.402</v>
+        <v>0.508</v>
       </c>
       <c r="T4">
         <v>0.0</v>
       </c>
       <c r="U4">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="V4">
-        <v>0.015</v>
+        <v>0.035</v>
       </c>
       <c r="W4">
-        <v>0.055</v>
+        <v>0.082</v>
       </c>
       <c r="X4">
-        <v>0.042</v>
+        <v>0.068</v>
       </c>
       <c r="Y4">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="Z4">
-        <v>0.073</v>
+        <v>0.093</v>
       </c>
       <c r="AA4">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="AB4">
-        <v>0.085</v>
+        <v>0.078</v>
       </c>
       <c r="AC4">
-        <v>0.11</v>
+        <v>0.084</v>
       </c>
       <c r="AD4">
-        <v>0.075</v>
+        <v>0.064</v>
       </c>
       <c r="AE4">
-        <v>0.072</v>
+        <v>0.07</v>
       </c>
       <c r="AF4">
+        <v>0.039</v>
+      </c>
+      <c r="AG4">
         <v>0.043</v>
       </c>
-      <c r="AG4">
-        <v>0.056</v>
-      </c>
       <c r="AH4">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="AI4">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AJ4">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="AK4">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="AL4">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AM4">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AN4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:40">
       <c r="A5">
-        <v>823390</v>
+        <v>823634</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>4.027</v>
+        <v>3.626</v>
       </c>
       <c r="F5">
-        <v>5.165</v>
+        <v>4.361</v>
       </c>
       <c r="G5">
-        <v>0.358</v>
+        <v>0.395</v>
       </c>
       <c r="H5">
-        <v>0.642</v>
+        <v>0.605</v>
       </c>
       <c r="I5">
-        <v>0.188</v>
+        <v>0.185</v>
       </c>
       <c r="J5">
-        <v>0.079</v>
+        <v>0.09</v>
       </c>
       <c r="K5">
-        <v>0.09</v>
+        <v>0.119</v>
       </c>
       <c r="L5">
-        <v>0.352</v>
+        <v>0.295</v>
       </c>
       <c r="M5">
-        <v>0.106</v>
+        <v>0.112</v>
       </c>
       <c r="N5">
-        <v>0.185</v>
+        <v>0.198</v>
       </c>
       <c r="O5">
-        <v>0.507</v>
+        <v>0.463</v>
       </c>
       <c r="P5">
-        <v>1.923</v>
+        <v>1.962</v>
       </c>
       <c r="Q5">
-        <v>3.061</v>
+        <v>2.434</v>
       </c>
       <c r="R5">
-        <v>0.283</v>
+        <v>0.359</v>
       </c>
       <c r="S5">
-        <v>0.565</v>
+        <v>0.478</v>
       </c>
       <c r="T5">
         <v>0.0</v>
       </c>
       <c r="U5">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="V5">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="W5">
-        <v>0.051</v>
+        <v>0.072</v>
       </c>
       <c r="X5">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="Y5">
-        <v>0.088</v>
+        <v>0.122</v>
       </c>
       <c r="Z5">
-        <v>0.078</v>
+        <v>0.084</v>
       </c>
       <c r="AA5">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="AB5">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AC5">
-        <v>0.093</v>
+        <v>0.103</v>
       </c>
       <c r="AD5">
-        <v>0.072</v>
+        <v>0.066</v>
       </c>
       <c r="AE5">
-        <v>0.085</v>
+        <v>0.081</v>
       </c>
       <c r="AF5">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="AG5">
-        <v>0.06</v>
+        <v>0.042</v>
       </c>
       <c r="AH5">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="AI5">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="AJ5">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
       <c r="AK5">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="AL5">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="AM5">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="AN5">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="6" spans="1:40">
       <c r="A6">
-        <v>823473</v>
+        <v>823714</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6">
-        <v>4.254</v>
+        <v>4.382</v>
       </c>
       <c r="F6">
-        <v>5.151</v>
+        <v>4.005</v>
       </c>
       <c r="G6">
-        <v>0.384</v>
+        <v>0.518</v>
       </c>
       <c r="H6">
-        <v>0.616</v>
+        <v>0.482</v>
       </c>
       <c r="I6">
-        <v>0.197</v>
+        <v>0.29</v>
       </c>
       <c r="J6">
-        <v>0.08</v>
+        <v>0.101</v>
       </c>
       <c r="K6">
-        <v>0.108</v>
+        <v>0.127</v>
       </c>
       <c r="L6">
-        <v>0.334</v>
+        <v>0.203</v>
       </c>
       <c r="M6">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="N6">
-        <v>0.18</v>
+        <v>0.165</v>
       </c>
       <c r="O6">
-        <v>0.511</v>
+        <v>0.468</v>
       </c>
       <c r="P6">
-        <v>2.207</v>
+        <v>2.385</v>
       </c>
       <c r="Q6">
-        <v>3.087</v>
+        <v>2.164</v>
       </c>
       <c r="R6">
-        <v>0.323</v>
+        <v>0.441</v>
       </c>
       <c r="S6">
-        <v>0.536</v>
+        <v>0.397</v>
       </c>
       <c r="T6">
         <v>0.0</v>
       </c>
       <c r="U6">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="V6">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W6">
-        <v>0.045</v>
+        <v>0.069</v>
       </c>
       <c r="X6">
-        <v>0.037</v>
+        <v>0.059</v>
       </c>
       <c r="Y6">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="Z6">
         <v>0.074</v>
       </c>
       <c r="AA6">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="AB6">
-        <v>0.067</v>
+        <v>0.086</v>
       </c>
       <c r="AC6">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="AD6">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="AE6">
-        <v>0.082</v>
+        <v>0.071</v>
       </c>
       <c r="AF6">
-        <v>0.062</v>
+        <v>0.046</v>
       </c>
       <c r="AG6">
-        <v>0.056</v>
+        <v>0.045</v>
       </c>
       <c r="AH6">
-        <v>0.039</v>
+        <v>0.028</v>
       </c>
       <c r="AI6">
-        <v>0.041</v>
+        <v>0.025</v>
       </c>
       <c r="AJ6">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
       <c r="AK6">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="AL6">
         <v>0.008</v>
       </c>
       <c r="AM6">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AN6">
-        <v>0.026</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="7" spans="1:40">
       <c r="A7">
-        <v>823636</v>
+        <v>823795</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>3.879</v>
+        <v>3.936</v>
       </c>
       <c r="F7">
-        <v>4.586</v>
+        <v>4.738</v>
       </c>
       <c r="G7">
-        <v>0.397</v>
+        <v>0.388</v>
       </c>
       <c r="H7">
-        <v>0.603</v>
+        <v>0.612</v>
       </c>
       <c r="I7">
-        <v>0.192</v>
+        <v>0.196</v>
       </c>
       <c r="J7">
-        <v>0.095</v>
+        <v>0.077</v>
       </c>
       <c r="K7">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="L7">
-        <v>0.301</v>
+        <v>0.307</v>
       </c>
       <c r="M7">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="N7">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="O7">
-        <v>0.475</v>
+        <v>0.494</v>
       </c>
       <c r="P7">
-        <v>2.078</v>
+        <v>1.991</v>
       </c>
       <c r="Q7">
-        <v>2.679</v>
+        <v>2.879</v>
       </c>
       <c r="R7">
-        <v>0.357</v>
+        <v>0.315</v>
       </c>
       <c r="S7">
-        <v>0.491</v>
+        <v>0.527</v>
       </c>
       <c r="T7">
         <v>0.0</v>
       </c>
       <c r="U7">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="V7">
+        <v>0.017</v>
+      </c>
+      <c r="W7">
+        <v>0.062</v>
+      </c>
+      <c r="X7">
+        <v>0.05</v>
+      </c>
+      <c r="Y7">
+        <v>0.097</v>
+      </c>
+      <c r="Z7">
+        <v>0.077</v>
+      </c>
+      <c r="AA7">
+        <v>0.12</v>
+      </c>
+      <c r="AB7">
+        <v>0.091</v>
+      </c>
+      <c r="AC7">
+        <v>0.1</v>
+      </c>
+      <c r="AD7">
+        <v>0.072</v>
+      </c>
+      <c r="AE7">
+        <v>0.076</v>
+      </c>
+      <c r="AF7">
+        <v>0.052</v>
+      </c>
+      <c r="AG7">
+        <v>0.044</v>
+      </c>
+      <c r="AH7">
+        <v>0.024</v>
+      </c>
+      <c r="AI7">
+        <v>0.034</v>
+      </c>
+      <c r="AJ7">
+        <v>0.014</v>
+      </c>
+      <c r="AK7">
+        <v>0.017</v>
+      </c>
+      <c r="AL7">
+        <v>0.009</v>
+      </c>
+      <c r="AM7">
+        <v>0.007</v>
+      </c>
+      <c r="AN7">
         <v>0.018</v>
-      </c>
-      <c r="W7">
-        <v>0.061</v>
-      </c>
-      <c r="X7">
-        <v>0.057</v>
-      </c>
-      <c r="Y7">
-        <v>0.115</v>
-      </c>
-      <c r="Z7">
-        <v>0.089</v>
-      </c>
-      <c r="AA7">
-        <v>0.108</v>
-      </c>
-      <c r="AB7">
-        <v>0.086</v>
-      </c>
-      <c r="AC7">
-        <v>0.102</v>
-      </c>
-      <c r="AD7">
-        <v>0.065</v>
-      </c>
-      <c r="AE7">
-        <v>0.07</v>
-      </c>
-      <c r="AF7">
-        <v>0.049</v>
-      </c>
-      <c r="AG7">
-        <v>0.048</v>
-      </c>
-      <c r="AH7">
-        <v>0.026</v>
-      </c>
-      <c r="AI7">
-        <v>0.024</v>
-      </c>
-      <c r="AJ7">
-        <v>0.016</v>
-      </c>
-      <c r="AK7">
-        <v>0.02</v>
-      </c>
-      <c r="AL7">
-        <v>0.014</v>
-      </c>
-      <c r="AM7">
-        <v>0.006</v>
-      </c>
-      <c r="AN7">
-        <v>0.01</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8">
-        <v>823716</v>
+        <v>824524</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8">
-        <v>4.39</v>
+        <v>4.817</v>
       </c>
       <c r="F8">
-        <v>4.161</v>
+        <v>4.916</v>
       </c>
       <c r="G8">
-        <v>0.506</v>
+        <v>0.466</v>
       </c>
       <c r="H8">
-        <v>0.494</v>
+        <v>0.534</v>
       </c>
       <c r="I8">
-        <v>0.274</v>
+        <v>0.256</v>
       </c>
       <c r="J8">
-        <v>0.104</v>
+        <v>0.095</v>
       </c>
       <c r="K8">
-        <v>0.129</v>
+        <v>0.115</v>
       </c>
       <c r="L8">
-        <v>0.223</v>
+        <v>0.256</v>
       </c>
       <c r="M8">
-        <v>0.107</v>
+        <v>0.103</v>
       </c>
       <c r="N8">
-        <v>0.164</v>
+        <v>0.174</v>
       </c>
       <c r="O8">
-        <v>0.474</v>
+        <v>0.524</v>
       </c>
       <c r="P8">
-        <v>2.21</v>
+        <v>2.798</v>
       </c>
       <c r="Q8">
-        <v>2.378</v>
+        <v>2.812</v>
       </c>
       <c r="R8">
-        <v>0.397</v>
+        <v>0.435</v>
       </c>
       <c r="S8">
-        <v>0.448</v>
+        <v>0.422</v>
       </c>
       <c r="T8">
         <v>0.0</v>
       </c>
       <c r="U8">
+        <v>0.009</v>
+      </c>
+      <c r="V8">
+        <v>0.01</v>
+      </c>
+      <c r="W8">
+        <v>0.035</v>
+      </c>
+      <c r="X8">
+        <v>0.044</v>
+      </c>
+      <c r="Y8">
+        <v>0.085</v>
+      </c>
+      <c r="Z8">
+        <v>0.062</v>
+      </c>
+      <c r="AA8">
+        <v>0.099</v>
+      </c>
+      <c r="AB8">
+        <v>0.076</v>
+      </c>
+      <c r="AC8">
+        <v>0.102</v>
+      </c>
+      <c r="AD8">
+        <v>0.081</v>
+      </c>
+      <c r="AE8">
+        <v>0.093</v>
+      </c>
+      <c r="AF8">
+        <v>0.054</v>
+      </c>
+      <c r="AG8">
+        <v>0.065</v>
+      </c>
+      <c r="AH8">
+        <v>0.042</v>
+      </c>
+      <c r="AI8">
+        <v>0.04</v>
+      </c>
+      <c r="AJ8">
+        <v>0.022</v>
+      </c>
+      <c r="AK8">
+        <v>0.027</v>
+      </c>
+      <c r="AL8">
+        <v>0.013</v>
+      </c>
+      <c r="AM8">
         <v>0.016</v>
       </c>
-      <c r="V8">
-        <v>0.018</v>
-      </c>
-      <c r="W8">
-        <v>0.061</v>
-      </c>
-      <c r="X8">
-        <v>0.058</v>
-      </c>
-      <c r="Y8">
-        <v>0.101</v>
-      </c>
-      <c r="Z8">
-        <v>0.079</v>
-      </c>
-      <c r="AA8">
-        <v>0.116</v>
-      </c>
-      <c r="AB8">
-        <v>0.082</v>
-      </c>
-      <c r="AC8">
-        <v>0.108</v>
-      </c>
-      <c r="AD8">
-        <v>0.071</v>
-      </c>
-      <c r="AE8">
-        <v>0.074</v>
-      </c>
-      <c r="AF8">
-        <v>0.049</v>
-      </c>
-      <c r="AG8">
-        <v>0.043</v>
-      </c>
-      <c r="AH8">
-        <v>0.037</v>
-      </c>
-      <c r="AI8">
-        <v>0.029</v>
-      </c>
-      <c r="AJ8">
-        <v>0.019</v>
-      </c>
-      <c r="AK8">
-        <v>0.016</v>
-      </c>
-      <c r="AL8">
-        <v>0.007</v>
-      </c>
-      <c r="AM8">
-        <v>0.006</v>
-      </c>
       <c r="AN8">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9">
-        <v>823798</v>
+        <v>824848</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9">
-        <v>4.325</v>
+        <v>5.105</v>
       </c>
       <c r="F9">
-        <v>4.746</v>
+        <v>5.099</v>
       </c>
       <c r="G9">
-        <v>0.425</v>
+        <v>0.468</v>
       </c>
       <c r="H9">
-        <v>0.575</v>
+        <v>0.532</v>
       </c>
       <c r="I9">
-        <v>0.225</v>
+        <v>0.275</v>
       </c>
       <c r="J9">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="K9">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="L9">
-        <v>0.297</v>
+        <v>0.262</v>
       </c>
       <c r="M9">
-        <v>0.107</v>
+        <v>0.112</v>
       </c>
       <c r="N9">
-        <v>0.17</v>
+        <v>0.158</v>
       </c>
       <c r="O9">
-        <v>0.514</v>
+        <v>0.563</v>
       </c>
       <c r="P9">
-        <v>2.284</v>
+        <v>3.071</v>
       </c>
       <c r="Q9">
-        <v>2.89</v>
+        <v>3.052</v>
       </c>
       <c r="R9">
-        <v>0.347</v>
+        <v>0.446</v>
       </c>
       <c r="S9">
-        <v>0.506</v>
+        <v>0.432</v>
       </c>
       <c r="T9">
         <v>0.0</v>
       </c>
       <c r="U9">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="V9">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="W9">
-        <v>0.059</v>
+        <v>0.03</v>
       </c>
       <c r="X9">
-        <v>0.046</v>
+        <v>0.037</v>
       </c>
       <c r="Y9">
-        <v>0.091</v>
+        <v>0.071</v>
       </c>
       <c r="Z9">
-        <v>0.074</v>
+        <v>0.06</v>
       </c>
       <c r="AA9">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="AB9">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="AC9">
-        <v>0.106</v>
+        <v>0.096</v>
       </c>
       <c r="AD9">
-        <v>0.071</v>
+        <v>0.082</v>
       </c>
       <c r="AE9">
-        <v>0.072</v>
+        <v>0.088</v>
       </c>
       <c r="AF9">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AG9">
-        <v>0.056</v>
+        <v>0.079</v>
       </c>
       <c r="AH9">
-        <v>0.03</v>
+        <v>0.048</v>
       </c>
       <c r="AI9">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="AJ9">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="AK9">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="AL9">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AM9">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="AN9">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="10" spans="1:40">
       <c r="A10">
-        <v>823956</v>
+        <v>824850</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10">
-        <v>3.285</v>
+        <v>4.558</v>
       </c>
       <c r="F10">
-        <v>4.603</v>
+        <v>5.796</v>
       </c>
       <c r="G10">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="H10">
-        <v>0.665</v>
+        <v>0.64</v>
       </c>
       <c r="I10">
-        <v>0.147</v>
+        <v>0.178</v>
       </c>
       <c r="J10">
         <v>0.077</v>
       </c>
       <c r="K10">
-        <v>0.111</v>
+        <v>0.105</v>
       </c>
       <c r="L10">
-        <v>0.344</v>
+        <v>0.359</v>
       </c>
       <c r="M10">
-        <v>0.124</v>
+        <v>0.105</v>
       </c>
       <c r="N10">
-        <v>0.196</v>
+        <v>0.176</v>
       </c>
       <c r="O10">
-        <v>0.453</v>
+        <v>0.572</v>
       </c>
       <c r="P10">
-        <v>1.602</v>
+        <v>2.569</v>
       </c>
       <c r="Q10">
-        <v>2.675</v>
+        <v>3.824</v>
       </c>
       <c r="R10">
-        <v>0.275</v>
+        <v>0.306</v>
       </c>
       <c r="S10">
-        <v>0.562</v>
+        <v>0.576</v>
       </c>
       <c r="T10">
-        <v>0.001</v>
+        <v>0.0</v>
       </c>
       <c r="U10">
-        <v>0.025</v>
+        <v>0.009</v>
       </c>
       <c r="V10">
-        <v>0.029</v>
+        <v>0.01</v>
       </c>
       <c r="W10">
-        <v>0.078</v>
+        <v>0.033</v>
       </c>
       <c r="X10">
-        <v>0.058</v>
+        <v>0.03</v>
       </c>
       <c r="Y10">
-        <v>0.116</v>
+        <v>0.055</v>
       </c>
       <c r="Z10">
-        <v>0.086</v>
+        <v>0.059</v>
       </c>
       <c r="AA10">
-        <v>0.124</v>
+        <v>0.099</v>
       </c>
       <c r="AB10">
-        <v>0.085</v>
+        <v>0.072</v>
       </c>
       <c r="AC10">
-        <v>0.097</v>
+        <v>0.108</v>
       </c>
       <c r="AD10">
-        <v>0.066</v>
+        <v>0.077</v>
       </c>
       <c r="AE10">
-        <v>0.054</v>
+        <v>0.09</v>
       </c>
       <c r="AF10">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="AG10">
-        <v>0.045</v>
+        <v>0.077</v>
       </c>
       <c r="AH10">
-        <v>0.024</v>
+        <v>0.046</v>
       </c>
       <c r="AI10">
-        <v>0.023</v>
+        <v>0.042</v>
       </c>
       <c r="AJ10">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="AK10">
-        <v>0.009</v>
+        <v>0.033</v>
       </c>
       <c r="AL10">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="AM10">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="AN10">
-        <v>0.008</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11" spans="1:40">
       <c r="A11">
-        <v>824447</v>
+        <v>824929</v>
       </c>
       <c r="B11" t="s">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E11">
-        <v>4.644</v>
+        <v>5.619</v>
       </c>
       <c r="F11">
-        <v>4.489</v>
+        <v>5.313</v>
       </c>
       <c r="G11">
-        <v>0.487</v>
+        <v>0.507</v>
       </c>
       <c r="H11">
-        <v>0.513</v>
+        <v>0.493</v>
       </c>
       <c r="I11">
-        <v>0.272</v>
+        <v>0.319</v>
       </c>
       <c r="J11">
-        <v>0.098</v>
+        <v>0.083</v>
       </c>
       <c r="K11">
-        <v>0.118</v>
+        <v>0.105</v>
       </c>
       <c r="L11">
-        <v>0.245</v>
+        <v>0.259</v>
       </c>
       <c r="M11">
-        <v>0.102</v>
+        <v>0.086</v>
       </c>
       <c r="N11">
-        <v>0.166</v>
+        <v>0.149</v>
       </c>
       <c r="O11">
-        <v>0.514</v>
+        <v>0.563</v>
       </c>
       <c r="P11">
-        <v>2.565</v>
+        <v>3.069</v>
       </c>
       <c r="Q11">
-        <v>2.551</v>
+        <v>3.011</v>
       </c>
       <c r="R11">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
       <c r="S11">
-        <v>0.424</v>
+        <v>0.432</v>
       </c>
       <c r="T11">
         <v>0.0</v>
       </c>
       <c r="U11">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="V11">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="W11">
-        <v>0.051</v>
+        <v>0.024</v>
       </c>
       <c r="X11">
-        <v>0.046</v>
+        <v>0.029</v>
       </c>
       <c r="Y11">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="Z11">
+        <v>0.047</v>
+      </c>
+      <c r="AA11">
+        <v>0.085</v>
+      </c>
+      <c r="AB11">
         <v>0.076</v>
       </c>
-      <c r="AA11">
-        <v>0.116</v>
-      </c>
-      <c r="AB11">
-        <v>0.08</v>
-      </c>
       <c r="AC11">
-        <v>0.109</v>
+        <v>0.101</v>
       </c>
       <c r="AD11">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
       <c r="AE11">
-        <v>0.082</v>
+        <v>0.086</v>
       </c>
       <c r="AF11">
-        <v>0.057</v>
+        <v>0.07</v>
       </c>
       <c r="AG11">
-        <v>0.057</v>
+        <v>0.073</v>
       </c>
       <c r="AH11">
-        <v>0.035</v>
+        <v>0.048</v>
       </c>
       <c r="AI11">
+        <v>0.055</v>
+      </c>
+      <c r="AJ11">
         <v>0.034</v>
       </c>
-      <c r="AJ11">
-        <v>0.017</v>
-      </c>
       <c r="AK11">
-        <v>0.017</v>
+        <v>0.036</v>
       </c>
       <c r="AL11">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="AM11">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AN11">
-        <v>0.02</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="12" spans="1:40">
       <c r="A12">
-        <v>824526</v>
+        <v>825016</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E12">
-        <v>4.134</v>
+        <v>4.742</v>
       </c>
       <c r="F12">
-        <v>4.854</v>
+        <v>5.941</v>
       </c>
       <c r="G12">
-        <v>0.401</v>
+        <v>0.369</v>
       </c>
       <c r="H12">
-        <v>0.599</v>
+        <v>0.631</v>
       </c>
       <c r="I12">
-        <v>0.201</v>
+        <v>0.193</v>
       </c>
       <c r="J12">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K12">
-        <v>0.11</v>
+        <v>0.096</v>
       </c>
       <c r="L12">
-        <v>0.299</v>
+        <v>0.365</v>
       </c>
       <c r="M12">
-        <v>0.125</v>
+        <v>0.104</v>
       </c>
       <c r="N12">
-        <v>0.175</v>
+        <v>0.162</v>
       </c>
       <c r="O12">
-        <v>0.471</v>
+        <v>0.555</v>
       </c>
       <c r="P12">
-        <v>1.954</v>
+        <v>2.455</v>
       </c>
       <c r="Q12">
-        <v>2.71</v>
+        <v>3.697</v>
       </c>
       <c r="R12">
-        <v>0.323</v>
+        <v>0.306</v>
       </c>
       <c r="S12">
-        <v>0.525</v>
+        <v>0.566</v>
       </c>
       <c r="T12">
         <v>0.0</v>
       </c>
       <c r="U12">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="V12">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="W12">
-        <v>0.056</v>
+        <v>0.025</v>
       </c>
       <c r="X12">
-        <v>0.054</v>
+        <v>0.025</v>
       </c>
       <c r="Y12">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="Z12">
-        <v>0.071</v>
+        <v>0.06</v>
       </c>
       <c r="AA12">
-        <v>0.113</v>
+        <v>0.083</v>
       </c>
       <c r="AB12">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="AC12">
+        <v>0.108</v>
+      </c>
+      <c r="AD12">
+        <v>0.075</v>
+      </c>
+      <c r="AE12">
         <v>0.102</v>
       </c>
-      <c r="AD12">
-        <v>0.08</v>
-      </c>
-      <c r="AE12">
-        <v>0.08</v>
-      </c>
       <c r="AF12">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="AG12">
-        <v>0.049</v>
+        <v>0.072</v>
       </c>
       <c r="AH12">
-        <v>0.035</v>
+        <v>0.043</v>
       </c>
       <c r="AI12">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="AJ12">
-        <v>0.021</v>
+        <v>0.032</v>
       </c>
       <c r="AK12">
-        <v>0.019</v>
+        <v>0.034</v>
       </c>
       <c r="AL12">
-        <v>0.009</v>
+        <v>0.023</v>
       </c>
       <c r="AM12">
-        <v>0.007</v>
+        <v>0.022</v>
       </c>
       <c r="AN12">
-        <v>0.024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40">
-      <c r="A13">
-        <v>824610</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13">
-        <v>4.966</v>
-      </c>
-      <c r="F13">
-        <v>3.503</v>
-      </c>
-      <c r="G13">
-        <v>0.629</v>
-      </c>
-      <c r="H13">
-        <v>0.371</v>
-      </c>
-      <c r="I13">
-        <v>0.395</v>
-      </c>
-      <c r="J13">
-        <v>0.1</v>
-      </c>
-      <c r="K13">
-        <v>0.134</v>
-      </c>
-      <c r="L13">
-        <v>0.145</v>
-      </c>
-      <c r="M13">
-        <v>0.076</v>
-      </c>
-      <c r="N13">
-        <v>0.15</v>
-      </c>
-      <c r="O13">
-        <v>0.484</v>
-      </c>
-      <c r="P13">
-        <v>2.76</v>
-      </c>
-      <c r="Q13">
-        <v>1.722</v>
-      </c>
-      <c r="R13">
-        <v>0.563</v>
-      </c>
-      <c r="S13">
-        <v>0.289</v>
-      </c>
-      <c r="T13">
-        <v>0.0</v>
-      </c>
-      <c r="U13">
-        <v>0.021</v>
-      </c>
-      <c r="V13">
-        <v>0.015</v>
-      </c>
-      <c r="W13">
-        <v>0.063</v>
-      </c>
-      <c r="X13">
-        <v>0.06</v>
-      </c>
-      <c r="Y13">
-        <v>0.111</v>
-      </c>
-      <c r="Z13">
-        <v>0.084</v>
-      </c>
-      <c r="AA13">
-        <v>0.115</v>
-      </c>
-      <c r="AB13">
-        <v>0.079</v>
-      </c>
-      <c r="AC13">
-        <v>0.106</v>
-      </c>
-      <c r="AD13">
-        <v>0.067</v>
-      </c>
-      <c r="AE13">
-        <v>0.067</v>
-      </c>
-      <c r="AF13">
-        <v>0.046</v>
-      </c>
-      <c r="AG13">
-        <v>0.049</v>
-      </c>
-      <c r="AH13">
-        <v>0.026</v>
-      </c>
-      <c r="AI13">
-        <v>0.026</v>
-      </c>
-      <c r="AJ13">
-        <v>0.019</v>
-      </c>
-      <c r="AK13">
-        <v>0.015</v>
-      </c>
-      <c r="AL13">
-        <v>0.006</v>
-      </c>
-      <c r="AM13">
-        <v>0.006</v>
-      </c>
-      <c r="AN13">
-        <v>0.018</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40">
-      <c r="A14">
-        <v>824849</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14">
-        <v>4.584</v>
-      </c>
-      <c r="F14">
-        <v>4.721</v>
-      </c>
-      <c r="G14">
-        <v>0.471</v>
-      </c>
-      <c r="H14">
-        <v>0.529</v>
-      </c>
-      <c r="I14">
-        <v>0.25</v>
-      </c>
-      <c r="J14">
-        <v>0.099</v>
-      </c>
-      <c r="K14">
-        <v>0.121</v>
-      </c>
-      <c r="L14">
-        <v>0.252</v>
-      </c>
-      <c r="M14">
-        <v>0.106</v>
-      </c>
-      <c r="N14">
-        <v>0.171</v>
-      </c>
-      <c r="O14">
-        <v>0.524</v>
-      </c>
-      <c r="P14">
-        <v>2.666</v>
-      </c>
-      <c r="Q14">
-        <v>2.694</v>
-      </c>
-      <c r="R14">
-        <v>0.432</v>
-      </c>
-      <c r="S14">
-        <v>0.425</v>
-      </c>
-      <c r="T14">
-        <v>0.0</v>
-      </c>
-      <c r="U14">
-        <v>0.012</v>
-      </c>
-      <c r="V14">
-        <v>0.016</v>
-      </c>
-      <c r="W14">
-        <v>0.051</v>
-      </c>
-      <c r="X14">
-        <v>0.046</v>
-      </c>
-      <c r="Y14">
-        <v>0.076</v>
-      </c>
-      <c r="Z14">
-        <v>0.071</v>
-      </c>
-      <c r="AA14">
-        <v>0.11</v>
-      </c>
-      <c r="AB14">
-        <v>0.077</v>
-      </c>
-      <c r="AC14">
-        <v>0.105</v>
-      </c>
-      <c r="AD14">
-        <v>0.07</v>
-      </c>
-      <c r="AE14">
-        <v>0.089</v>
-      </c>
-      <c r="AF14">
-        <v>0.053</v>
-      </c>
-      <c r="AG14">
-        <v>0.065</v>
-      </c>
-      <c r="AH14">
-        <v>0.037</v>
-      </c>
-      <c r="AI14">
-        <v>0.035</v>
-      </c>
-      <c r="AJ14">
-        <v>0.023</v>
-      </c>
-      <c r="AK14">
-        <v>0.02</v>
-      </c>
-      <c r="AL14">
-        <v>0.012</v>
-      </c>
-      <c r="AM14">
-        <v>0.013</v>
-      </c>
-      <c r="AN14">
-        <v>0.019</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40">
-      <c r="A15">
-        <v>824931</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15">
-        <v>5.112</v>
-      </c>
-      <c r="F15">
-        <v>4.7</v>
-      </c>
-      <c r="G15">
-        <v>0.522</v>
-      </c>
-      <c r="H15">
-        <v>0.478</v>
-      </c>
-      <c r="I15">
-        <v>0.298</v>
-      </c>
-      <c r="J15">
-        <v>0.101</v>
-      </c>
-      <c r="K15">
-        <v>0.123</v>
-      </c>
-      <c r="L15">
-        <v>0.222</v>
-      </c>
-      <c r="M15">
-        <v>0.097</v>
-      </c>
-      <c r="N15">
-        <v>0.158</v>
-      </c>
-      <c r="O15">
-        <v>0.522</v>
-      </c>
-      <c r="P15">
-        <v>2.878</v>
-      </c>
-      <c r="Q15">
-        <v>2.587</v>
-      </c>
-      <c r="R15">
-        <v>0.466</v>
-      </c>
-      <c r="S15">
-        <v>0.395</v>
-      </c>
-      <c r="T15">
-        <v>0.0</v>
-      </c>
-      <c r="U15">
-        <v>0.01</v>
-      </c>
-      <c r="V15">
-        <v>0.012</v>
-      </c>
-      <c r="W15">
         <v>0.042</v>
-      </c>
-      <c r="X15">
-        <v>0.035</v>
-      </c>
-      <c r="Y15">
-        <v>0.075</v>
-      </c>
-      <c r="Z15">
-        <v>0.059</v>
-      </c>
-      <c r="AA15">
-        <v>0.103</v>
-      </c>
-      <c r="AB15">
-        <v>0.077</v>
-      </c>
-      <c r="AC15">
-        <v>0.108</v>
-      </c>
-      <c r="AD15">
-        <v>0.073</v>
-      </c>
-      <c r="AE15">
-        <v>0.086</v>
-      </c>
-      <c r="AF15">
-        <v>0.062</v>
-      </c>
-      <c r="AG15">
-        <v>0.065</v>
-      </c>
-      <c r="AH15">
-        <v>0.042</v>
-      </c>
-      <c r="AI15">
-        <v>0.041</v>
-      </c>
-      <c r="AJ15">
-        <v>0.031</v>
-      </c>
-      <c r="AK15">
-        <v>0.023</v>
-      </c>
-      <c r="AL15">
-        <v>0.015</v>
-      </c>
-      <c r="AM15">
-        <v>0.016</v>
-      </c>
-      <c r="AN15">
-        <v>0.024</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40">
-      <c r="A16">
-        <v>825017</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16">
-        <v>4.899</v>
-      </c>
-      <c r="F16">
-        <v>4.705</v>
-      </c>
-      <c r="G16">
-        <v>0.494</v>
-      </c>
-      <c r="H16">
-        <v>0.506</v>
-      </c>
-      <c r="I16">
-        <v>0.285</v>
-      </c>
-      <c r="J16">
-        <v>0.094</v>
-      </c>
-      <c r="K16">
-        <v>0.115</v>
-      </c>
-      <c r="L16">
-        <v>0.234</v>
-      </c>
-      <c r="M16">
-        <v>0.103</v>
-      </c>
-      <c r="N16">
-        <v>0.17</v>
-      </c>
-      <c r="O16">
-        <v>0.522</v>
-      </c>
-      <c r="P16">
-        <v>2.549</v>
-      </c>
-      <c r="Q16">
-        <v>2.573</v>
-      </c>
-      <c r="R16">
-        <v>0.428</v>
-      </c>
-      <c r="S16">
-        <v>0.423</v>
-      </c>
-      <c r="T16">
-        <v>0.0</v>
-      </c>
-      <c r="U16">
-        <v>0.011</v>
-      </c>
-      <c r="V16">
-        <v>0.011</v>
-      </c>
-      <c r="W16">
-        <v>0.046</v>
-      </c>
-      <c r="X16">
-        <v>0.04</v>
-      </c>
-      <c r="Y16">
-        <v>0.081</v>
-      </c>
-      <c r="Z16">
-        <v>0.072</v>
-      </c>
-      <c r="AA16">
-        <v>0.108</v>
-      </c>
-      <c r="AB16">
-        <v>0.081</v>
-      </c>
-      <c r="AC16">
-        <v>0.099</v>
-      </c>
-      <c r="AD16">
-        <v>0.068</v>
-      </c>
-      <c r="AE16">
-        <v>0.077</v>
-      </c>
-      <c r="AF16">
-        <v>0.055</v>
-      </c>
-      <c r="AG16">
-        <v>0.066</v>
-      </c>
-      <c r="AH16">
-        <v>0.043</v>
-      </c>
-      <c r="AI16">
-        <v>0.033</v>
-      </c>
-      <c r="AJ16">
-        <v>0.027</v>
-      </c>
-      <c r="AK16">
-        <v>0.029</v>
-      </c>
-      <c r="AL16">
-        <v>0.013</v>
-      </c>
-      <c r="AM16">
-        <v>0.015</v>
-      </c>
-      <c r="AN16">
-        <v>0.025</v>
       </c>
     </row>
   </sheetData>

--- a/data/BallparkPal_Games.xlsx
+++ b/data/BallparkPal_Games.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
   <si>
     <t>GamePk</t>
   </si>
@@ -137,58 +137,94 @@
     <t>Runs20</t>
   </si>
   <si>
-    <t>2026-04-30</t>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>LAD</t>
   </si>
   <si>
     <t>STL</t>
   </si>
   <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
     <t>PIT</t>
   </si>
   <si>
-    <t xml:space="preserve">SF </t>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>MIN</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>WAS</t>
+    <t>MIA</t>
   </si>
   <si>
     <t>NYM</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>MIN</t>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>COL</t>
   </si>
   <si>
     <t>ARI</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>CIN</t>
+    <t>CHC</t>
   </si>
   <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>BAL</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KC </t>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>CLE</t>
   </si>
   <si>
     <t>ATH</t>
@@ -531,7 +567,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -658,7 +694,7 @@
     </row>
     <row r="2" spans="1:40">
       <c r="A2">
-        <v>823391</v>
+        <v>822744</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -670,117 +706,117 @@
         <v>42</v>
       </c>
       <c r="E2">
-        <v>3.155</v>
+        <v>5.722</v>
       </c>
       <c r="F2">
-        <v>4.49</v>
+        <v>3.893</v>
       </c>
       <c r="G2">
-        <v>0.341</v>
+        <v>0.662</v>
       </c>
       <c r="H2">
-        <v>0.659</v>
+        <v>0.338</v>
       </c>
       <c r="I2">
-        <v>0.144</v>
+        <v>0.428</v>
       </c>
       <c r="J2">
-        <v>0.083</v>
+        <v>0.109</v>
       </c>
       <c r="K2">
-        <v>0.113</v>
+        <v>0.124</v>
       </c>
       <c r="L2">
-        <v>0.346</v>
+        <v>0.138</v>
       </c>
       <c r="M2">
-        <v>0.126</v>
+        <v>0.067</v>
       </c>
       <c r="N2">
-        <v>0.188</v>
+        <v>0.133</v>
       </c>
       <c r="O2">
-        <v>0.43</v>
+        <v>0.505</v>
       </c>
       <c r="P2">
-        <v>1.35</v>
+        <v>3.234</v>
       </c>
       <c r="Q2">
-        <v>2.556</v>
+        <v>1.944</v>
       </c>
       <c r="R2">
-        <v>0.253</v>
+        <v>0.595</v>
       </c>
       <c r="S2">
-        <v>0.57</v>
+        <v>0.269</v>
       </c>
       <c r="T2">
         <v>0.0</v>
       </c>
       <c r="U2">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="V2">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
       <c r="W2">
-        <v>0.087</v>
+        <v>0.045</v>
       </c>
       <c r="X2">
-        <v>0.061</v>
+        <v>0.04</v>
       </c>
       <c r="Y2">
-        <v>0.122</v>
+        <v>0.078</v>
       </c>
       <c r="Z2">
-        <v>0.094</v>
+        <v>0.072</v>
       </c>
       <c r="AA2">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="AB2">
-        <v>0.082</v>
+        <v>0.084</v>
       </c>
       <c r="AC2">
-        <v>0.092</v>
+        <v>0.098</v>
       </c>
       <c r="AD2">
-        <v>0.059</v>
+        <v>0.071</v>
       </c>
       <c r="AE2">
-        <v>0.065</v>
+        <v>0.085</v>
       </c>
       <c r="AF2">
+        <v>0.05</v>
+      </c>
+      <c r="AG2">
+        <v>0.068</v>
+      </c>
+      <c r="AH2">
+        <v>0.041</v>
+      </c>
+      <c r="AI2">
         <v>0.04</v>
       </c>
-      <c r="AG2">
-        <v>0.037</v>
-      </c>
-      <c r="AH2">
-        <v>0.024</v>
-      </c>
-      <c r="AI2">
-        <v>0.021</v>
-      </c>
       <c r="AJ2">
-        <v>0.009</v>
+        <v>0.022</v>
       </c>
       <c r="AK2">
+        <v>0.029</v>
+      </c>
+      <c r="AL2">
+        <v>0.014</v>
+      </c>
+      <c r="AM2">
         <v>0.011</v>
       </c>
-      <c r="AL2">
-        <v>0.006</v>
-      </c>
-      <c r="AM2">
-        <v>0.004</v>
-      </c>
       <c r="AN2">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="3" spans="1:40">
       <c r="A3">
-        <v>823471</v>
+        <v>822990</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -792,1025 +828,1025 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>4.782</v>
+        <v>4.165</v>
       </c>
       <c r="F3">
-        <v>5.568</v>
+        <v>4.639</v>
       </c>
       <c r="G3">
-        <v>0.395</v>
+        <v>0.426</v>
       </c>
       <c r="H3">
-        <v>0.605</v>
+        <v>0.574</v>
       </c>
       <c r="I3">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="J3">
-        <v>0.071</v>
+        <v>0.085</v>
       </c>
       <c r="K3">
-        <v>0.099</v>
+        <v>0.117</v>
       </c>
       <c r="L3">
-        <v>0.344</v>
+        <v>0.292</v>
       </c>
       <c r="M3">
-        <v>0.094</v>
+        <v>0.114</v>
       </c>
       <c r="N3">
         <v>0.168</v>
       </c>
       <c r="O3">
-        <v>0.557</v>
+        <v>0.48</v>
       </c>
       <c r="P3">
-        <v>2.722</v>
+        <v>2.24</v>
       </c>
       <c r="Q3">
-        <v>3.438</v>
+        <v>2.767</v>
       </c>
       <c r="R3">
-        <v>0.362</v>
+        <v>0.356</v>
       </c>
       <c r="S3">
-        <v>0.524</v>
+        <v>0.494</v>
       </c>
       <c r="T3">
         <v>0.0</v>
       </c>
       <c r="U3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V3">
+        <v>0.019</v>
+      </c>
+      <c r="W3">
+        <v>0.056</v>
+      </c>
+      <c r="X3">
+        <v>0.054</v>
+      </c>
+      <c r="Y3">
+        <v>0.089</v>
+      </c>
+      <c r="Z3">
+        <v>0.077</v>
+      </c>
+      <c r="AA3">
+        <v>0.109</v>
+      </c>
+      <c r="AB3">
+        <v>0.081</v>
+      </c>
+      <c r="AC3">
+        <v>0.11</v>
+      </c>
+      <c r="AD3">
+        <v>0.07</v>
+      </c>
+      <c r="AE3">
+        <v>0.076</v>
+      </c>
+      <c r="AF3">
+        <v>0.052</v>
+      </c>
+      <c r="AG3">
+        <v>0.053</v>
+      </c>
+      <c r="AH3">
+        <v>0.038</v>
+      </c>
+      <c r="AI3">
+        <v>0.033</v>
+      </c>
+      <c r="AJ3">
+        <v>0.017</v>
+      </c>
+      <c r="AK3">
+        <v>0.017</v>
+      </c>
+      <c r="AL3">
+        <v>0.006</v>
+      </c>
+      <c r="AM3">
         <v>0.008</v>
       </c>
-      <c r="W3">
-        <v>0.029</v>
-      </c>
-      <c r="X3">
-        <v>0.033</v>
-      </c>
-      <c r="Y3">
-        <v>0.066</v>
-      </c>
-      <c r="Z3">
-        <v>0.054</v>
-      </c>
-      <c r="AA3">
-        <v>0.099</v>
-      </c>
-      <c r="AB3">
-        <v>0.065</v>
-      </c>
-      <c r="AC3">
-        <v>0.103</v>
-      </c>
-      <c r="AD3">
-        <v>0.08</v>
-      </c>
-      <c r="AE3">
-        <v>0.084</v>
-      </c>
-      <c r="AF3">
-        <v>0.063</v>
-      </c>
-      <c r="AG3">
-        <v>0.084</v>
-      </c>
-      <c r="AH3">
-        <v>0.044</v>
-      </c>
-      <c r="AI3">
-        <v>0.05</v>
-      </c>
-      <c r="AJ3">
-        <v>0.03</v>
-      </c>
-      <c r="AK3">
-        <v>0.026</v>
-      </c>
-      <c r="AL3">
-        <v>0.021</v>
-      </c>
-      <c r="AM3">
-        <v>0.014</v>
-      </c>
       <c r="AN3">
-        <v>0.035</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="4" spans="1:40">
       <c r="A4">
-        <v>823472</v>
+        <v>823066</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4">
-        <v>3.638</v>
+        <v>5.095</v>
       </c>
       <c r="F4">
-        <v>4.264</v>
+        <v>3.68</v>
       </c>
       <c r="G4">
-        <v>0.399</v>
+        <v>0.633</v>
       </c>
       <c r="H4">
-        <v>0.601</v>
+        <v>0.367</v>
       </c>
       <c r="I4">
-        <v>0.181</v>
+        <v>0.38</v>
       </c>
       <c r="J4">
-        <v>0.104</v>
+        <v>0.111</v>
       </c>
       <c r="K4">
-        <v>0.113</v>
+        <v>0.142</v>
       </c>
       <c r="L4">
-        <v>0.279</v>
+        <v>0.144</v>
       </c>
       <c r="M4">
-        <v>0.124</v>
+        <v>0.077</v>
       </c>
       <c r="N4">
-        <v>0.198</v>
+        <v>0.146</v>
       </c>
       <c r="O4">
-        <v>0.418</v>
+        <v>0.51</v>
       </c>
       <c r="P4">
-        <v>1.839</v>
+        <v>2.891</v>
       </c>
       <c r="Q4">
-        <v>2.385</v>
+        <v>1.995</v>
       </c>
       <c r="R4">
-        <v>0.326</v>
+        <v>0.544</v>
       </c>
       <c r="S4">
-        <v>0.508</v>
+        <v>0.314</v>
       </c>
       <c r="T4">
         <v>0.0</v>
       </c>
       <c r="U4">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="V4">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="W4">
-        <v>0.082</v>
+        <v>0.053</v>
       </c>
       <c r="X4">
+        <v>0.046</v>
+      </c>
+      <c r="Y4">
+        <v>0.097</v>
+      </c>
+      <c r="Z4">
+        <v>0.084</v>
+      </c>
+      <c r="AA4">
+        <v>0.13</v>
+      </c>
+      <c r="AB4">
+        <v>0.079</v>
+      </c>
+      <c r="AC4">
+        <v>0.108</v>
+      </c>
+      <c r="AD4">
         <v>0.068</v>
       </c>
-      <c r="Y4">
-        <v>0.107</v>
-      </c>
-      <c r="Z4">
-        <v>0.093</v>
-      </c>
-      <c r="AA4">
-        <v>0.12</v>
-      </c>
-      <c r="AB4">
-        <v>0.078</v>
-      </c>
-      <c r="AC4">
+      <c r="AE4">
         <v>0.084</v>
       </c>
-      <c r="AD4">
-        <v>0.064</v>
-      </c>
-      <c r="AE4">
-        <v>0.07</v>
-      </c>
       <c r="AF4">
-        <v>0.039</v>
+        <v>0.05</v>
       </c>
       <c r="AG4">
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
       <c r="AH4">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="AI4">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="AJ4">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="AK4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AL4">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AM4">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="AN4">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="5" spans="1:40">
       <c r="A5">
-        <v>823634</v>
+        <v>823146</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>3.626</v>
+        <v>3.033</v>
       </c>
       <c r="F5">
-        <v>4.361</v>
+        <v>3.966</v>
       </c>
       <c r="G5">
-        <v>0.395</v>
+        <v>0.364</v>
       </c>
       <c r="H5">
-        <v>0.605</v>
+        <v>0.636</v>
       </c>
       <c r="I5">
-        <v>0.185</v>
+        <v>0.155</v>
       </c>
       <c r="J5">
-        <v>0.09</v>
+        <v>0.087</v>
       </c>
       <c r="K5">
-        <v>0.119</v>
+        <v>0.122</v>
       </c>
       <c r="L5">
         <v>0.295</v>
       </c>
       <c r="M5">
-        <v>0.112</v>
+        <v>0.12</v>
       </c>
       <c r="N5">
-        <v>0.198</v>
+        <v>0.221</v>
       </c>
       <c r="O5">
-        <v>0.463</v>
+        <v>0.425</v>
       </c>
       <c r="P5">
-        <v>1.962</v>
+        <v>1.486</v>
       </c>
       <c r="Q5">
-        <v>2.434</v>
+        <v>2.291</v>
       </c>
       <c r="R5">
-        <v>0.359</v>
+        <v>0.298</v>
       </c>
       <c r="S5">
-        <v>0.478</v>
+        <v>0.522</v>
       </c>
       <c r="T5">
         <v>0.0</v>
       </c>
       <c r="U5">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="V5">
-        <v>0.025</v>
+        <v>0.038</v>
       </c>
       <c r="W5">
-        <v>0.072</v>
+        <v>0.109</v>
       </c>
       <c r="X5">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="Y5">
-        <v>0.122</v>
+        <v>0.145</v>
       </c>
       <c r="Z5">
         <v>0.084</v>
       </c>
       <c r="AA5">
-        <v>0.114</v>
+        <v>0.125</v>
       </c>
       <c r="AB5">
-        <v>0.079</v>
+        <v>0.086</v>
       </c>
       <c r="AC5">
-        <v>0.103</v>
+        <v>0.087</v>
       </c>
       <c r="AD5">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="AE5">
-        <v>0.081</v>
+        <v>0.05</v>
       </c>
       <c r="AF5">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="AG5">
-        <v>0.042</v>
+        <v>0.027</v>
       </c>
       <c r="AH5">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="AI5">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="AJ5">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AK5">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AL5">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AM5">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AN5">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="6" spans="1:40">
       <c r="A6">
-        <v>823714</v>
+        <v>823309</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <v>4.382</v>
+        <v>4.149</v>
       </c>
       <c r="F6">
-        <v>4.005</v>
+        <v>4.767</v>
       </c>
       <c r="G6">
-        <v>0.518</v>
+        <v>0.416</v>
       </c>
       <c r="H6">
-        <v>0.482</v>
+        <v>0.584</v>
       </c>
       <c r="I6">
-        <v>0.29</v>
+        <v>0.205</v>
       </c>
       <c r="J6">
-        <v>0.101</v>
+        <v>0.094</v>
       </c>
       <c r="K6">
-        <v>0.127</v>
+        <v>0.117</v>
       </c>
       <c r="L6">
-        <v>0.203</v>
+        <v>0.295</v>
       </c>
       <c r="M6">
-        <v>0.113</v>
+        <v>0.109</v>
       </c>
       <c r="N6">
-        <v>0.165</v>
+        <v>0.181</v>
       </c>
       <c r="O6">
-        <v>0.468</v>
+        <v>0.489</v>
       </c>
       <c r="P6">
-        <v>2.385</v>
+        <v>2.41</v>
       </c>
       <c r="Q6">
-        <v>2.164</v>
+        <v>2.61</v>
       </c>
       <c r="R6">
+        <v>0.4</v>
+      </c>
+      <c r="S6">
         <v>0.441</v>
-      </c>
-      <c r="S6">
-        <v>0.397</v>
       </c>
       <c r="T6">
         <v>0.0</v>
       </c>
       <c r="U6">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="V6">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="W6">
-        <v>0.069</v>
+        <v>0.053</v>
       </c>
       <c r="X6">
-        <v>0.059</v>
+        <v>0.047</v>
       </c>
       <c r="Y6">
-        <v>0.104</v>
+        <v>0.089</v>
       </c>
       <c r="Z6">
         <v>0.074</v>
       </c>
       <c r="AA6">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="AB6">
-        <v>0.086</v>
+        <v>0.08</v>
       </c>
       <c r="AC6">
-        <v>0.111</v>
+        <v>0.099</v>
       </c>
       <c r="AD6">
-        <v>0.08</v>
+        <v>0.071</v>
       </c>
       <c r="AE6">
-        <v>0.071</v>
+        <v>0.078</v>
       </c>
       <c r="AF6">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="AG6">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="AH6">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="AI6">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="AJ6">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="AK6">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AL6">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AM6">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="AN6">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="7" spans="1:40">
       <c r="A7">
-        <v>823795</v>
+        <v>823389</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7">
-        <v>3.936</v>
+        <v>4.275</v>
       </c>
       <c r="F7">
-        <v>4.738</v>
+        <v>4.478</v>
       </c>
       <c r="G7">
-        <v>0.388</v>
+        <v>0.454</v>
       </c>
       <c r="H7">
-        <v>0.612</v>
+        <v>0.546</v>
       </c>
       <c r="I7">
-        <v>0.196</v>
+        <v>0.234</v>
       </c>
       <c r="J7">
-        <v>0.077</v>
+        <v>0.094</v>
       </c>
       <c r="K7">
-        <v>0.115</v>
+        <v>0.126</v>
       </c>
       <c r="L7">
-        <v>0.307</v>
+        <v>0.253</v>
       </c>
       <c r="M7">
-        <v>0.12</v>
+        <v>0.103</v>
       </c>
       <c r="N7">
-        <v>0.186</v>
+        <v>0.189</v>
       </c>
       <c r="O7">
-        <v>0.494</v>
+        <v>0.464</v>
       </c>
       <c r="P7">
-        <v>1.991</v>
+        <v>2.271</v>
       </c>
       <c r="Q7">
-        <v>2.879</v>
+        <v>2.639</v>
       </c>
       <c r="R7">
-        <v>0.315</v>
+        <v>0.374</v>
       </c>
       <c r="S7">
-        <v>0.527</v>
+        <v>0.466</v>
       </c>
       <c r="T7">
         <v>0.0</v>
       </c>
       <c r="U7">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="V7">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="W7">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="X7">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="Y7">
-        <v>0.097</v>
+        <v>0.093</v>
       </c>
       <c r="Z7">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="AA7">
         <v>0.12</v>
       </c>
       <c r="AB7">
-        <v>0.091</v>
+        <v>0.077</v>
       </c>
       <c r="AC7">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="AD7">
-        <v>0.072</v>
+        <v>0.065</v>
       </c>
       <c r="AE7">
-        <v>0.076</v>
+        <v>0.082</v>
       </c>
       <c r="AF7">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AG7">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="AH7">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="AI7">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="AJ7">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="AK7">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="AL7">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="AM7">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="AN7">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8">
-        <v>824524</v>
+        <v>823557</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8">
-        <v>4.817</v>
+        <v>4.487</v>
       </c>
       <c r="F8">
-        <v>4.916</v>
+        <v>4.842</v>
       </c>
       <c r="G8">
-        <v>0.466</v>
+        <v>0.426</v>
       </c>
       <c r="H8">
-        <v>0.534</v>
+        <v>0.574</v>
       </c>
       <c r="I8">
-        <v>0.256</v>
+        <v>0.232</v>
       </c>
       <c r="J8">
-        <v>0.095</v>
+        <v>0.078</v>
       </c>
       <c r="K8">
-        <v>0.115</v>
+        <v>0.117</v>
       </c>
       <c r="L8">
-        <v>0.256</v>
+        <v>0.277</v>
       </c>
       <c r="M8">
-        <v>0.103</v>
+        <v>0.116</v>
       </c>
       <c r="N8">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="O8">
-        <v>0.524</v>
+        <v>0.526</v>
       </c>
       <c r="P8">
-        <v>2.798</v>
+        <v>2.384</v>
       </c>
       <c r="Q8">
-        <v>2.812</v>
+        <v>2.923</v>
       </c>
       <c r="R8">
-        <v>0.435</v>
+        <v>0.362</v>
       </c>
       <c r="S8">
-        <v>0.422</v>
+        <v>0.495</v>
       </c>
       <c r="T8">
         <v>0.0</v>
       </c>
       <c r="U8">
+        <v>0.016</v>
+      </c>
+      <c r="V8">
         <v>0.009</v>
       </c>
-      <c r="V8">
-        <v>0.01</v>
-      </c>
       <c r="W8">
-        <v>0.035</v>
+        <v>0.046</v>
       </c>
       <c r="X8">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="Y8">
-        <v>0.085</v>
+        <v>0.091</v>
       </c>
       <c r="Z8">
-        <v>0.062</v>
+        <v>0.066</v>
       </c>
       <c r="AA8">
-        <v>0.099</v>
+        <v>0.117</v>
       </c>
       <c r="AB8">
-        <v>0.076</v>
+        <v>0.09</v>
       </c>
       <c r="AC8">
-        <v>0.102</v>
+        <v>0.092</v>
       </c>
       <c r="AD8">
-        <v>0.081</v>
+        <v>0.068</v>
       </c>
       <c r="AE8">
-        <v>0.093</v>
+        <v>0.08</v>
       </c>
       <c r="AF8">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="AG8">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="AH8">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="AI8">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="AJ8">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="AK8">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="AL8">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AM8">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AN8">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9">
-        <v>824848</v>
+        <v>823713</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E9">
-        <v>5.105</v>
+        <v>4.481</v>
       </c>
       <c r="F9">
-        <v>5.099</v>
+        <v>4.994</v>
       </c>
       <c r="G9">
-        <v>0.468</v>
+        <v>0.439</v>
       </c>
       <c r="H9">
-        <v>0.532</v>
+        <v>0.561</v>
       </c>
       <c r="I9">
-        <v>0.275</v>
+        <v>0.228</v>
       </c>
       <c r="J9">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="K9">
-        <v>0.103</v>
+        <v>0.118</v>
       </c>
       <c r="L9">
-        <v>0.262</v>
+        <v>0.301</v>
       </c>
       <c r="M9">
-        <v>0.112</v>
+        <v>0.096</v>
       </c>
       <c r="N9">
-        <v>0.158</v>
+        <v>0.165</v>
       </c>
       <c r="O9">
-        <v>0.563</v>
+        <v>0.549</v>
       </c>
       <c r="P9">
-        <v>3.071</v>
+        <v>2.47</v>
       </c>
       <c r="Q9">
-        <v>3.052</v>
+        <v>3.176</v>
       </c>
       <c r="R9">
-        <v>0.446</v>
+        <v>0.353</v>
       </c>
       <c r="S9">
-        <v>0.432</v>
+        <v>0.502</v>
       </c>
       <c r="T9">
         <v>0.0</v>
       </c>
       <c r="U9">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="V9">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="W9">
-        <v>0.03</v>
+        <v>0.047</v>
       </c>
       <c r="X9">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="Y9">
-        <v>0.071</v>
+        <v>0.083</v>
       </c>
       <c r="Z9">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="AA9">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="AB9">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="AC9">
-        <v>0.096</v>
+        <v>0.109</v>
       </c>
       <c r="AD9">
-        <v>0.082</v>
+        <v>0.066</v>
       </c>
       <c r="AE9">
-        <v>0.088</v>
+        <v>0.092</v>
       </c>
       <c r="AF9">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="AG9">
-        <v>0.079</v>
+        <v>0.069</v>
       </c>
       <c r="AH9">
-        <v>0.048</v>
+        <v>0.035</v>
       </c>
       <c r="AI9">
-        <v>0.042</v>
+        <v>0.039</v>
       </c>
       <c r="AJ9">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AK9">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="AL9">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="AM9">
+        <v>0.011</v>
+      </c>
+      <c r="AN9">
         <v>0.017</v>
-      </c>
-      <c r="AN9">
-        <v>0.034</v>
       </c>
     </row>
     <row r="10" spans="1:40">
       <c r="A10">
-        <v>824850</v>
+        <v>823877</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E10">
-        <v>4.558</v>
+        <v>4.51</v>
       </c>
       <c r="F10">
-        <v>5.796</v>
+        <v>3.319</v>
       </c>
       <c r="G10">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="H10">
-        <v>0.64</v>
+        <v>0.39</v>
       </c>
       <c r="I10">
-        <v>0.178</v>
+        <v>0.349</v>
       </c>
       <c r="J10">
-        <v>0.077</v>
+        <v>0.114</v>
       </c>
       <c r="K10">
-        <v>0.105</v>
+        <v>0.147</v>
       </c>
       <c r="L10">
-        <v>0.359</v>
+        <v>0.137</v>
       </c>
       <c r="M10">
-        <v>0.105</v>
+        <v>0.086</v>
       </c>
       <c r="N10">
-        <v>0.176</v>
+        <v>0.167</v>
       </c>
       <c r="O10">
-        <v>0.572</v>
+        <v>0.482</v>
       </c>
       <c r="P10">
-        <v>2.569</v>
+        <v>2.495</v>
       </c>
       <c r="Q10">
-        <v>3.824</v>
+        <v>1.686</v>
       </c>
       <c r="R10">
-        <v>0.306</v>
+        <v>0.533</v>
       </c>
       <c r="S10">
-        <v>0.576</v>
+        <v>0.297</v>
       </c>
       <c r="T10">
         <v>0.0</v>
       </c>
       <c r="U10">
+        <v>0.025</v>
+      </c>
+      <c r="V10">
+        <v>0.025</v>
+      </c>
+      <c r="W10">
+        <v>0.083</v>
+      </c>
+      <c r="X10">
+        <v>0.075</v>
+      </c>
+      <c r="Y10">
+        <v>0.116</v>
+      </c>
+      <c r="Z10">
+        <v>0.079</v>
+      </c>
+      <c r="AA10">
+        <v>0.127</v>
+      </c>
+      <c r="AB10">
+        <v>0.088</v>
+      </c>
+      <c r="AC10">
+        <v>0.098</v>
+      </c>
+      <c r="AD10">
+        <v>0.057</v>
+      </c>
+      <c r="AE10">
+        <v>0.061</v>
+      </c>
+      <c r="AF10">
+        <v>0.036</v>
+      </c>
+      <c r="AG10">
+        <v>0.036</v>
+      </c>
+      <c r="AH10">
+        <v>0.025</v>
+      </c>
+      <c r="AI10">
+        <v>0.024</v>
+      </c>
+      <c r="AJ10">
+        <v>0.013</v>
+      </c>
+      <c r="AK10">
+        <v>0.013</v>
+      </c>
+      <c r="AL10">
+        <v>0.005</v>
+      </c>
+      <c r="AM10">
+        <v>0.006</v>
+      </c>
+      <c r="AN10">
         <v>0.009</v>
-      </c>
-      <c r="V10">
-        <v>0.01</v>
-      </c>
-      <c r="W10">
-        <v>0.033</v>
-      </c>
-      <c r="X10">
-        <v>0.03</v>
-      </c>
-      <c r="Y10">
-        <v>0.055</v>
-      </c>
-      <c r="Z10">
-        <v>0.059</v>
-      </c>
-      <c r="AA10">
-        <v>0.099</v>
-      </c>
-      <c r="AB10">
-        <v>0.072</v>
-      </c>
-      <c r="AC10">
-        <v>0.108</v>
-      </c>
-      <c r="AD10">
-        <v>0.077</v>
-      </c>
-      <c r="AE10">
-        <v>0.09</v>
-      </c>
-      <c r="AF10">
-        <v>0.057</v>
-      </c>
-      <c r="AG10">
-        <v>0.077</v>
-      </c>
-      <c r="AH10">
-        <v>0.046</v>
-      </c>
-      <c r="AI10">
-        <v>0.042</v>
-      </c>
-      <c r="AJ10">
-        <v>0.031</v>
-      </c>
-      <c r="AK10">
-        <v>0.033</v>
-      </c>
-      <c r="AL10">
-        <v>0.017</v>
-      </c>
-      <c r="AM10">
-        <v>0.019</v>
-      </c>
-      <c r="AN10">
-        <v>0.036</v>
       </c>
     </row>
     <row r="11" spans="1:40">
       <c r="A11">
-        <v>824929</v>
+        <v>824041</v>
       </c>
       <c r="B11" t="s">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11">
-        <v>5.619</v>
+        <v>5.316</v>
       </c>
       <c r="F11">
-        <v>5.313</v>
+        <v>5.129</v>
       </c>
       <c r="G11">
-        <v>0.507</v>
+        <v>0.491</v>
       </c>
       <c r="H11">
-        <v>0.493</v>
+        <v>0.509</v>
       </c>
       <c r="I11">
-        <v>0.319</v>
+        <v>0.285</v>
       </c>
       <c r="J11">
-        <v>0.083</v>
+        <v>0.097</v>
       </c>
       <c r="K11">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="L11">
-        <v>0.259</v>
+        <v>0.254</v>
       </c>
       <c r="M11">
-        <v>0.086</v>
+        <v>0.089</v>
       </c>
       <c r="N11">
-        <v>0.149</v>
+        <v>0.166</v>
       </c>
       <c r="O11">
-        <v>0.563</v>
+        <v>0.558</v>
       </c>
       <c r="P11">
-        <v>3.069</v>
+        <v>2.918</v>
       </c>
       <c r="Q11">
-        <v>3.011</v>
+        <v>3.07</v>
       </c>
       <c r="R11">
-        <v>0.439</v>
+        <v>0.42</v>
       </c>
       <c r="S11">
-        <v>0.432</v>
+        <v>0.458</v>
       </c>
       <c r="T11">
         <v>0.0</v>
@@ -1822,180 +1858,668 @@
         <v>0.007</v>
       </c>
       <c r="W11">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
       <c r="X11">
         <v>0.029</v>
       </c>
       <c r="Y11">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="Z11">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="AA11">
-        <v>0.085</v>
+        <v>0.094</v>
       </c>
       <c r="AB11">
-        <v>0.076</v>
+        <v>0.07</v>
       </c>
       <c r="AC11">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AD11">
         <v>0.067</v>
       </c>
       <c r="AE11">
-        <v>0.086</v>
+        <v>0.094</v>
       </c>
       <c r="AF11">
-        <v>0.07</v>
+        <v>0.064</v>
       </c>
       <c r="AG11">
-        <v>0.073</v>
+        <v>0.071</v>
       </c>
       <c r="AH11">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="AI11">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="AJ11">
+        <v>0.031</v>
+      </c>
+      <c r="AK11">
         <v>0.034</v>
       </c>
-      <c r="AK11">
-        <v>0.036</v>
-      </c>
       <c r="AL11">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="AM11">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="AN11">
-        <v>0.054</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="12" spans="1:40">
       <c r="A12">
-        <v>825016</v>
+        <v>824287</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E12">
-        <v>4.742</v>
+        <v>5.329</v>
       </c>
       <c r="F12">
-        <v>5.941</v>
+        <v>5.18</v>
       </c>
       <c r="G12">
-        <v>0.369</v>
+        <v>0.486</v>
       </c>
       <c r="H12">
-        <v>0.631</v>
+        <v>0.514</v>
       </c>
       <c r="I12">
-        <v>0.193</v>
+        <v>0.289</v>
       </c>
       <c r="J12">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="K12">
-        <v>0.096</v>
+        <v>0.107</v>
       </c>
       <c r="L12">
-        <v>0.365</v>
+        <v>0.254</v>
       </c>
       <c r="M12">
-        <v>0.104</v>
+        <v>0.088</v>
       </c>
       <c r="N12">
-        <v>0.162</v>
+        <v>0.171</v>
       </c>
       <c r="O12">
-        <v>0.555</v>
+        <v>0.558</v>
       </c>
       <c r="P12">
-        <v>2.455</v>
+        <v>3.105</v>
       </c>
       <c r="Q12">
-        <v>3.697</v>
+        <v>3.182</v>
       </c>
       <c r="R12">
-        <v>0.306</v>
+        <v>0.431</v>
       </c>
       <c r="S12">
-        <v>0.566</v>
+        <v>0.446</v>
       </c>
       <c r="T12">
         <v>0.0</v>
       </c>
       <c r="U12">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="V12">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="W12">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="X12">
         <v>0.025</v>
       </c>
       <c r="Y12">
-        <v>0.06</v>
+        <v>0.068</v>
       </c>
       <c r="Z12">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="AA12">
-        <v>0.083</v>
+        <v>0.086</v>
       </c>
       <c r="AB12">
-        <v>0.075</v>
+        <v>0.069</v>
       </c>
       <c r="AC12">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="AD12">
         <v>0.075</v>
       </c>
       <c r="AE12">
+        <v>0.097</v>
+      </c>
+      <c r="AF12">
+        <v>0.07</v>
+      </c>
+      <c r="AG12">
+        <v>0.077</v>
+      </c>
+      <c r="AH12">
+        <v>0.04</v>
+      </c>
+      <c r="AI12">
+        <v>0.045</v>
+      </c>
+      <c r="AJ12">
+        <v>0.029</v>
+      </c>
+      <c r="AK12">
+        <v>0.031</v>
+      </c>
+      <c r="AL12">
+        <v>0.019</v>
+      </c>
+      <c r="AM12">
+        <v>0.021</v>
+      </c>
+      <c r="AN12">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13">
+        <v>824366</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>7.148</v>
+      </c>
+      <c r="F13">
+        <v>5.947</v>
+      </c>
+      <c r="G13">
+        <v>0.585</v>
+      </c>
+      <c r="H13">
+        <v>0.415</v>
+      </c>
+      <c r="I13">
+        <v>0.393</v>
+      </c>
+      <c r="J13">
+        <v>0.095</v>
+      </c>
+      <c r="K13">
+        <v>0.097</v>
+      </c>
+      <c r="L13">
+        <v>0.213</v>
+      </c>
+      <c r="M13">
+        <v>0.075</v>
+      </c>
+      <c r="N13">
+        <v>0.127</v>
+      </c>
+      <c r="O13">
+        <v>0.643</v>
+      </c>
+      <c r="P13">
+        <v>4.136</v>
+      </c>
+      <c r="Q13">
+        <v>3.437</v>
+      </c>
+      <c r="R13">
+        <v>0.522</v>
+      </c>
+      <c r="S13">
+        <v>0.37</v>
+      </c>
+      <c r="T13">
+        <v>0.0</v>
+      </c>
+      <c r="U13">
+        <v>0.002</v>
+      </c>
+      <c r="V13">
+        <v>0.002</v>
+      </c>
+      <c r="W13">
+        <v>0.014</v>
+      </c>
+      <c r="X13">
+        <v>0.013</v>
+      </c>
+      <c r="Y13">
+        <v>0.028</v>
+      </c>
+      <c r="Z13">
+        <v>0.027</v>
+      </c>
+      <c r="AA13">
+        <v>0.054</v>
+      </c>
+      <c r="AB13">
+        <v>0.049</v>
+      </c>
+      <c r="AC13">
+        <v>0.078</v>
+      </c>
+      <c r="AD13">
+        <v>0.064</v>
+      </c>
+      <c r="AE13">
+        <v>0.089</v>
+      </c>
+      <c r="AF13">
+        <v>0.076</v>
+      </c>
+      <c r="AG13">
+        <v>0.08</v>
+      </c>
+      <c r="AH13">
+        <v>0.059</v>
+      </c>
+      <c r="AI13">
+        <v>0.071</v>
+      </c>
+      <c r="AJ13">
+        <v>0.051</v>
+      </c>
+      <c r="AK13">
+        <v>0.06</v>
+      </c>
+      <c r="AL13">
+        <v>0.033</v>
+      </c>
+      <c r="AM13">
+        <v>0.037</v>
+      </c>
+      <c r="AN13">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14">
+        <v>824686</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14">
+        <v>3.946</v>
+      </c>
+      <c r="F14">
+        <v>4.209</v>
+      </c>
+      <c r="G14">
+        <v>0.446</v>
+      </c>
+      <c r="H14">
+        <v>0.554</v>
+      </c>
+      <c r="I14">
+        <v>0.23</v>
+      </c>
+      <c r="J14">
+        <v>0.094</v>
+      </c>
+      <c r="K14">
+        <v>0.123</v>
+      </c>
+      <c r="L14">
+        <v>0.252</v>
+      </c>
+      <c r="M14">
+        <v>0.106</v>
+      </c>
+      <c r="N14">
+        <v>0.196</v>
+      </c>
+      <c r="O14">
+        <v>0.447</v>
+      </c>
+      <c r="P14">
+        <v>2.005</v>
+      </c>
+      <c r="Q14">
+        <v>2.338</v>
+      </c>
+      <c r="R14">
+        <v>0.369</v>
+      </c>
+      <c r="S14">
+        <v>0.461</v>
+      </c>
+      <c r="T14">
+        <v>0.0</v>
+      </c>
+      <c r="U14">
+        <v>0.024</v>
+      </c>
+      <c r="V14">
+        <v>0.025</v>
+      </c>
+      <c r="W14">
+        <v>0.078</v>
+      </c>
+      <c r="X14">
+        <v>0.062</v>
+      </c>
+      <c r="Y14">
+        <v>0.107</v>
+      </c>
+      <c r="Z14">
+        <v>0.084</v>
+      </c>
+      <c r="AA14">
+        <v>0.116</v>
+      </c>
+      <c r="AB14">
+        <v>0.067</v>
+      </c>
+      <c r="AC14">
+        <v>0.106</v>
+      </c>
+      <c r="AD14">
+        <v>0.067</v>
+      </c>
+      <c r="AE14">
+        <v>0.075</v>
+      </c>
+      <c r="AF14">
+        <v>0.04</v>
+      </c>
+      <c r="AG14">
+        <v>0.046</v>
+      </c>
+      <c r="AH14">
+        <v>0.021</v>
+      </c>
+      <c r="AI14">
+        <v>0.031</v>
+      </c>
+      <c r="AJ14">
+        <v>0.018</v>
+      </c>
+      <c r="AK14">
+        <v>0.013</v>
+      </c>
+      <c r="AL14">
+        <v>0.007</v>
+      </c>
+      <c r="AM14">
+        <v>0.004</v>
+      </c>
+      <c r="AN14">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15">
+        <v>824772</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15">
+        <v>5.542</v>
+      </c>
+      <c r="F15">
+        <v>5.007</v>
+      </c>
+      <c r="G15">
+        <v>0.516</v>
+      </c>
+      <c r="H15">
+        <v>0.484</v>
+      </c>
+      <c r="I15">
+        <v>0.313</v>
+      </c>
+      <c r="J15">
+        <v>0.09</v>
+      </c>
+      <c r="K15">
+        <v>0.113</v>
+      </c>
+      <c r="L15">
+        <v>0.228</v>
+      </c>
+      <c r="M15">
+        <v>0.099</v>
+      </c>
+      <c r="N15">
+        <v>0.157</v>
+      </c>
+      <c r="O15">
+        <v>0.587</v>
+      </c>
+      <c r="P15">
+        <v>3.205</v>
+      </c>
+      <c r="Q15">
+        <v>2.908</v>
+      </c>
+      <c r="R15">
+        <v>0.47</v>
+      </c>
+      <c r="S15">
+        <v>0.398</v>
+      </c>
+      <c r="T15">
+        <v>0.0</v>
+      </c>
+      <c r="U15">
+        <v>0.006</v>
+      </c>
+      <c r="V15">
+        <v>0.007</v>
+      </c>
+      <c r="W15">
+        <v>0.032</v>
+      </c>
+      <c r="X15">
+        <v>0.032</v>
+      </c>
+      <c r="Y15">
+        <v>0.06</v>
+      </c>
+      <c r="Z15">
+        <v>0.048</v>
+      </c>
+      <c r="AA15">
+        <v>0.09</v>
+      </c>
+      <c r="AB15">
+        <v>0.079</v>
+      </c>
+      <c r="AC15">
+        <v>0.101</v>
+      </c>
+      <c r="AD15">
+        <v>0.073</v>
+      </c>
+      <c r="AE15">
+        <v>0.101</v>
+      </c>
+      <c r="AF15">
+        <v>0.062</v>
+      </c>
+      <c r="AG15">
+        <v>0.071</v>
+      </c>
+      <c r="AH15">
+        <v>0.052</v>
+      </c>
+      <c r="AI15">
+        <v>0.044</v>
+      </c>
+      <c r="AJ15">
+        <v>0.032</v>
+      </c>
+      <c r="AK15">
+        <v>0.032</v>
+      </c>
+      <c r="AL15">
+        <v>0.017</v>
+      </c>
+      <c r="AM15">
+        <v>0.021</v>
+      </c>
+      <c r="AN15">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
+      <c r="A16">
+        <v>825012</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16">
+        <v>4.567</v>
+      </c>
+      <c r="F16">
+        <v>5.023</v>
+      </c>
+      <c r="G16">
+        <v>0.432</v>
+      </c>
+      <c r="H16">
+        <v>0.568</v>
+      </c>
+      <c r="I16">
+        <v>0.237</v>
+      </c>
+      <c r="J16">
+        <v>0.087</v>
+      </c>
+      <c r="K16">
+        <v>0.107</v>
+      </c>
+      <c r="L16">
+        <v>0.306</v>
+      </c>
+      <c r="M16">
+        <v>0.105</v>
+      </c>
+      <c r="N16">
+        <v>0.157</v>
+      </c>
+      <c r="O16">
+        <v>0.48</v>
+      </c>
+      <c r="P16">
+        <v>2.243</v>
+      </c>
+      <c r="Q16">
+        <v>2.858</v>
+      </c>
+      <c r="R16">
+        <v>0.356</v>
+      </c>
+      <c r="S16">
+        <v>0.492</v>
+      </c>
+      <c r="T16">
+        <v>0.0</v>
+      </c>
+      <c r="U16">
+        <v>0.012</v>
+      </c>
+      <c r="V16">
+        <v>0.015</v>
+      </c>
+      <c r="W16">
+        <v>0.041</v>
+      </c>
+      <c r="X16">
+        <v>0.042</v>
+      </c>
+      <c r="Y16">
+        <v>0.077</v>
+      </c>
+      <c r="Z16">
+        <v>0.065</v>
+      </c>
+      <c r="AA16">
+        <v>0.112</v>
+      </c>
+      <c r="AB16">
+        <v>0.085</v>
+      </c>
+      <c r="AC16">
         <v>0.102</v>
       </c>
-      <c r="AF12">
-        <v>0.057</v>
-      </c>
-      <c r="AG12">
-        <v>0.072</v>
-      </c>
-      <c r="AH12">
-        <v>0.043</v>
-      </c>
-      <c r="AI12">
-        <v>0.05</v>
-      </c>
-      <c r="AJ12">
-        <v>0.032</v>
-      </c>
-      <c r="AK12">
-        <v>0.034</v>
-      </c>
-      <c r="AL12">
-        <v>0.023</v>
-      </c>
-      <c r="AM12">
+      <c r="AD16">
+        <v>0.073</v>
+      </c>
+      <c r="AE16">
+        <v>0.085</v>
+      </c>
+      <c r="AF16">
+        <v>0.052</v>
+      </c>
+      <c r="AG16">
+        <v>0.063</v>
+      </c>
+      <c r="AH16">
+        <v>0.037</v>
+      </c>
+      <c r="AI16">
+        <v>0.036</v>
+      </c>
+      <c r="AJ16">
+        <v>0.025</v>
+      </c>
+      <c r="AK16">
         <v>0.022</v>
       </c>
-      <c r="AN12">
-        <v>0.042</v>
+      <c r="AL16">
+        <v>0.015</v>
+      </c>
+      <c r="AM16">
+        <v>0.01</v>
+      </c>
+      <c r="AN16">
+        <v>0.031</v>
       </c>
     </row>
   </sheetData>
